--- a/runac/demo/MPE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -228,8 +228,8 @@
         <t>Modalidad de cuidado
 Entorno o tipo de acogimiento alternativo formal en el cual se encuentra inserto el NyA.
 Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Provincia".
+Máximo 22 caracteres.
+Elegir de la lista "Modalidad de cuidado".
 No es obligatorio.</t>
       </text>
     </comment>
@@ -8480,58 +8480,58 @@
   </mergeCells>
   <dataValidations count="18">
     <dataValidation sqref="B4:B203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Provincia&quot;." promptTitle="Provincia" prompt="Jurisdicción político-territorial que dicta y ejecuta la medida excepcional." type="list">
-      <formula1>LISTAS!$H$2:$H$26</formula1>
+      <formula1>LISTAS!$I$2:$I$26</formula1>
     </dataValidation>
     <dataValidation sqref="C4:C203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Modalidad de cuidado&quot;." promptTitle="Modalidad de cuidado" prompt="Entorno o tipo de acogimiento alternativo formal en el cual se encuentra inserto el NyA." type="list">
-      <formula1>LISTAS!$H$2:$H$26</formula1>
+      <formula1>LISTAS!$D$2:$D$5</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Género&quot;." promptTitle="Género" prompt="Identidad de género autopercibida por el NyA." type="list">
       <formula1>LISTAS!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="N4:N203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;País de nacimiento&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$247</formula1>
+      <formula1>LISTAS!$F$2:$F$247</formula1>
     </dataValidation>
     <dataValidation sqref="Q4:Q203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Asiste a institución educativa?&quot;." promptTitle="¿Asiste a institución educativa?" prompt="Indica si asiste de forma activa e inscrita a algún establecimiento oficial de educación inicial, primaria, secundaria o educación especial." type="list">
       <formula1>LISTAS!$A$2:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="S4:S203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Enfermedad crónica&quot;." promptTitle="Enfermedad crónica" prompt="Indica si el NyA padece alguna condición médica crónica que requiera tratamiento continuo certificado (ej. asma, diabetes, VIH)." type="list">
-      <formula1>LISTAS!$G$2:$G$4</formula1>
+      <formula1>LISTAS!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="T4:T203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Consumo problemático de sustancias&quot;." promptTitle="Consumo problemático de sustanci" prompt="Indica si presenta consumo recurrente u problemático de sustancias adictivas diagnosticado o en abordaje." type="list">
-      <formula1>LISTAS!$G$2:$G$4</formula1>
+      <formula1>LISTAS!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="U4:U203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Presenta alguna discapacidad?&quot;." promptTitle="¿Presenta alguna discapacidad?" prompt="Indica si el NyA tiene una discapacidad física, intelectual, auditiva, visual, etc." type="list">
-      <formula1>LISTAS!$G$2:$G$4</formula1>
+      <formula1>LISTAS!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de discapacidad&quot;." promptTitle="Tipo de discapacidad" prompt="Categoría de la discapacidad predominante del NyA." type="list">
-      <formula1>LISTAS!$J$2:$J$8</formula1>
+      <formula1>LISTAS!$K$2:$K$8</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Posee CUD?&quot;." promptTitle="¿Posee CUD?" prompt="Indica si el NyA cuenta con el Certificado Único de Discapacidad oficial nacional vigente." type="list">
-      <formula1>LISTAS!$F$2:$F$5</formula1>
+      <formula1>LISTAS!$G$2:$G$5</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cobertura salud&quot;." promptTitle="Cobertura salud" prompt="Tipo de cobertura médica de la que goza el NyA." type="list">
       <formula1>LISTAS!$B$2:$B$4</formula1>
     </dataValidation>
     <dataValidation sqref="Y4:Y203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Pertenece a pueblo originario?&quot;." promptTitle="¿Pertenece a pueblo originario?" prompt="Indica si el NyA se autoreconoce o pertenece a una comunidad de pueblos originarios de Argentina." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>LISTAS!$J$2:$J$4</formula1>
     </dataValidation>
     <dataValidation sqref="AA4:AA203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Tiene hijos/as?&quot;." promptTitle="¿Tiene hijos/as?" prompt="Indica si el NyA es padre o madre." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>LISTAS!$J$2:$J$4</formula1>
     </dataValidation>
     <dataValidation sqref="AH4:AH203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Origen de la demanda&quot;." promptTitle="Origen de la demanda" prompt="Canal que alertó de la vulneración de derechos inicial que dio origen a la MPE." type="list">
-      <formula1>LISTAS!$D$2:$D$7</formula1>
+      <formula1>LISTAS!$E$2:$E$7</formula1>
     </dataValidation>
     <dataValidation sqref="AK4:AK203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de proyecto de restitución&quot;." promptTitle="Tipo de proyecto de restitución" prompt="Línea de acción priorizada del Plan Especial de Restitución (PER) vigente para el NyA." type="list">
-      <formula1>LISTAS!$K$2:$K$5</formula1>
+      <formula1>LISTAS!$L$2:$L$5</formula1>
     </dataValidation>
     <dataValidation sqref="AL4:AL203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Elevación dictamen MPE a juzgado&quot;." promptTitle="Elevación dictamen MPE a juzgado" prompt="Indica si el dictamen de control de legalidad de la MPE fue elevado al Juzgado de Familia." type="list">
-      <formula1>LISTAS!$G$2:$G$4</formula1>
+      <formula1>LISTAS!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="AM4:AM203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Decreto judicial de adoptabilidad&quot;." promptTitle="Decreto judicial de adoptabilida" prompt="Indica si existe sentencia judicial firme decretando el estado de adoptabilidad del NyA" type="list">
-      <formula1>LISTAS!$G$2:$G$4</formula1>
+      <formula1>LISTAS!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="AN4:AN203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Solicitud inclusión proy. autonomía&quot;." promptTitle="Solicitud inclusión proy. autono" prompt="Indica si se ha gestionado e incorporado al NyA al Programa de Acompañamiento para el Egreso (PAE) o iniciativa provincial de autonomía." type="list">
-      <formula1>LISTAS!$G$2:$G$4</formula1>
+      <formula1>LISTAS!$H$2:$H$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8614,7 +8614,7 @@
       <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Entorno o tipo de acogimiento alternativo formal en el cual se encuentra inserto el NyA.
-Debe elegirse un valor de la lista "Provincia".</t>
+Debe elegirse un valor de la lista "Modalidad de cuidado".</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K247"/>
+  <dimension ref="A1:L247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -9148,6 +9148,7 @@
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9168,40 +9169,45 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
+          <t>Modalidad de cuidado</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
           <t>Origen de la demanda</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>País de nacimiento</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>¿Posee CUD?</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>¿Presenta alguna discapacidad?</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Sí / No / Sin datos</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Tipo de discapacidad</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Tipo de proyecto de restitución</t>
         </is>
@@ -9225,40 +9231,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Alojamiento formal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Encuentro espontáneo</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Buenos Aires</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Visual</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Reintegro familiar</t>
         </is>
@@ -9282,40 +9293,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Familia ampliada</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Educación</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Afganistán</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>CABA</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Auditiva</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Adopción</t>
         </is>
@@ -9334,40 +9350,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Familia de acogimiento</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Salud</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Albania</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>En trámite</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Catamarca</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Mental</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Autonomía</t>
         </is>
@@ -9376,1854 +9397,1859 @@
     <row r="5">
       <c r="D5" t="inlineStr">
         <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Policía</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Alemania</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Chaco</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Motora</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Juzgado</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Algeria</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Chubut</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Visceral</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Andorra</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Córdoba</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Angola</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Corrientes</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Anguila</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Entre Ríos</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Antártida</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Formosa</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Antigua y Barbuda</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Jujuy</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Antillas Neerlandesas</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>La Pampa</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Arabia Saudita</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>La Rioja</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Mendoza</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Armenia</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Misiones</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Neuquén</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Río Negro</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Salta</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Azerbayán</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>San Juan</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Bélgica</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>San Luis</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Bahamas</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Santa Cruz</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Bahrein</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Santa Fe</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Bangladesh</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Santiago del Estero</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Barbados</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Tierra del Fuego</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Belice</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Tucumán</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Benín</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Bhután</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Bielorrusia</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Birmania</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Bolivia</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Bosnia y Herzegovina</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Botsuana</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Brunéi</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Bulgaria</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Burkina Faso</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Burundi</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Cabo Verde</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Camboya</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Camerún</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Canadá</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Chad</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Chipre</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Ciudad del Vaticano</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Comoras</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Congo</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Corea del Norte</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Corea del Sur</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Costa de Marfil</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Croacia</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Cuba</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Dinamarca</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Dominica</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Egipto</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>El Salvador</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Emiratos Árabes Unidos</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Eritrea</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Eslovaquia</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Eslovenia</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>España</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Estados Unidos de América</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Etiopía</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Filipinas</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Finlandia</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Fiyi</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Francia</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Gabón</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Gambia</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Gibraltar</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Grecia</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Groenlandia</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Guadalupe</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Guam</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Guatemala</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Guayana Francesa</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Guernsey</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Guinea</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Guinea Ecuatorial</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Guinea-Bissau</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Guyana</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Haití</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Honduras</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Hong kong</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Hungría</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>Irán</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Irlanda</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Isla Bouvet</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>Isla de Man</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Isla de Navidad</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>Isla Norfolk</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Islandia</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Islas Bermudas</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="E105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Islas Caimán</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="E106" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Islas Cocos (Keeling)</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="E107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Islas Cook</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="E108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>Islas de Åland</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="E109" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Islas Feroe</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="E110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Islas Georgias del Sur y Sandwich del Sur</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="E111" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>Islas Heard y McDonald</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="E112" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Islas Maldivas</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="E113" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Islas Malvinas</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="E114" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>Islas Marianas del Norte</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="E115" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>Islas Marshall</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="E116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Islas Pitcairn</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="E117" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>Islas Salomón</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="E118" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Islas Turcas y Caicos</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="E119" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Islas Ultramarinas Menores de Estados Unidos</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="E120" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Islas Vírgenes Británicas</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="E121" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Islas Vírgenes de los Estados Unidos</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="E122" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Israel</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="E123" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="E124" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>Jamaica</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="E125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="E126" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Jersey</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="E127" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Jordania</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="E128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Kazajistán</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="E129" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>Kenia</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="E130" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>Kirgizstán</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="E131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Kiribati</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="E132" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Kuwait</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="E133" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Líbano</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="E134" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Laos</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="E135" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Lesoto</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="E136" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>Letonia</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="E137" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Liberia</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="E138" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>Libia</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="E139" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Liechtenstein</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="E140" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Lituania</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="E141" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>Luxemburgo</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="E142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="E143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Mónaco</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="E144" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Macao</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="E145" t="inlineStr">
+      <c r="F145" t="inlineStr">
         <is>
           <t>Macedônia</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="E146" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>Madagascar</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="E147" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>Malasia</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="E148" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Malawi</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="E149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Mali</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="E150" t="inlineStr">
+      <c r="F150" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="E151" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>Marruecos</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="E152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Martinica</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="E153" t="inlineStr">
+      <c r="F153" t="inlineStr">
         <is>
           <t>Mauricio</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="E154" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>Mauritania</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="E155" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Mayotte</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="E156" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Micronesia</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="E157" t="inlineStr">
+      <c r="F157" t="inlineStr">
         <is>
           <t>Moldavia</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="E158" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Mongolia</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="E159" t="inlineStr">
+      <c r="F159" t="inlineStr">
         <is>
           <t>Montenegro</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="E160" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Montserrat</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="E161" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Mozambique</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="E162" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>Namibia</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="E163" t="inlineStr">
+      <c r="F163" t="inlineStr">
         <is>
           <t>Nauru</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="E164" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Nepal</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="E165" t="inlineStr">
+      <c r="F165" t="inlineStr">
         <is>
           <t>Nicaragua</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="E166" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>Niger</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="E167" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="E168" t="inlineStr">
+      <c r="F168" t="inlineStr">
         <is>
           <t>Niue</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="E169" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Noruega</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="E170" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Nueva Caledonia</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="E171" t="inlineStr">
+      <c r="F171" t="inlineStr">
         <is>
           <t>Nueva Zelanda</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="E172" t="inlineStr">
+      <c r="F172" t="inlineStr">
         <is>
           <t>Omán</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="E173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Países Bajos</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="E174" t="inlineStr">
+      <c r="F174" t="inlineStr">
         <is>
           <t>Pakistán</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="E175" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>Palau</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="E176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Palestina</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="E177" t="inlineStr">
+      <c r="F177" t="inlineStr">
         <is>
           <t>Panamá</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="E178" t="inlineStr">
+      <c r="F178" t="inlineStr">
         <is>
           <t>Papúa Nueva Guinea</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="E179" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="E180" t="inlineStr">
+      <c r="F180" t="inlineStr">
         <is>
           <t>Perú</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="E181" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>Polinesia Francesa</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="E182" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Polonia</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="E183" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="E184" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>Puerto Rico</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="E185" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="E186" t="inlineStr">
+      <c r="F186" t="inlineStr">
         <is>
           <t>Reino Unido</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="E187" t="inlineStr">
+      <c r="F187" t="inlineStr">
         <is>
           <t>República Centroafricana</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="E188" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>República Checa</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="E189" t="inlineStr">
+      <c r="F189" t="inlineStr">
         <is>
           <t>República Dominicana</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="E190" t="inlineStr">
+      <c r="F190" t="inlineStr">
         <is>
           <t>Reunión</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="E191" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>Ruanda</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="E192" t="inlineStr">
+      <c r="F192" t="inlineStr">
         <is>
           <t>Rumanía</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="E193" t="inlineStr">
+      <c r="F193" t="inlineStr">
         <is>
           <t>Rusia</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="E194" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>Sahara Occidental</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="E195" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>Samoa</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="E196" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Samoa Americana</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="E197" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>San Bartolomé</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="E198" t="inlineStr">
+      <c r="F198" t="inlineStr">
         <is>
           <t>San Cristóbal y Nieves</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="E199" t="inlineStr">
+      <c r="F199" t="inlineStr">
         <is>
           <t>San Marino</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="E200" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>San Martín (Francia)</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="E201" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>San Pedro y Miquelón</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="E202" t="inlineStr">
+      <c r="F202" t="inlineStr">
         <is>
           <t>San Vicente y las Granadinas</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="E203" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>Santa Elena</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="E204" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>Santa Lucía</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="E205" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>Santo Tomé y Príncipe</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="E206" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="E207" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>Serbia</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="E208" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>Seychelles</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="E209" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>Sierra Leona</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="E210" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>Singapur</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="E211" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>Siria</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="E212" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>Somalia</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="E213" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>Sri lanka</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="E214" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>Sudáfrica</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="E215" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Sudán</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="E216" t="inlineStr">
+      <c r="F216" t="inlineStr">
         <is>
           <t>Suecia</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="E217" t="inlineStr">
+      <c r="F217" t="inlineStr">
         <is>
           <t>Suiza</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="E218" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>Surinám</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="E219" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>Svalbard y Jan Mayen</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="E220" t="inlineStr">
+      <c r="F220" t="inlineStr">
         <is>
           <t>Swazilandia</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="E221" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>Tadjikistán</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="E222" t="inlineStr">
+      <c r="F222" t="inlineStr">
         <is>
           <t>Tailandia</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="E223" t="inlineStr">
+      <c r="F223" t="inlineStr">
         <is>
           <t>Taiwán</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="E224" t="inlineStr">
+      <c r="F224" t="inlineStr">
         <is>
           <t>Tanzania</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="E225" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>Territorio Británico del Océano Índico</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="E226" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>Territorios Australes y Antárticas Franceses</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="E227" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>Timor Oriental</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="E228" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="E229" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>Tokelau</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="E230" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>Tonga</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="E231" t="inlineStr">
+      <c r="F231" t="inlineStr">
         <is>
           <t>Trinidad y Tobago</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="E232" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>Tunez</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="E233" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>Turkmenistán</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="E234" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>Turquía</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="E235" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>Tuvalu</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="E236" t="inlineStr">
+      <c r="F236" t="inlineStr">
         <is>
           <t>Ucrania</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="E237" t="inlineStr">
+      <c r="F237" t="inlineStr">
         <is>
           <t>Uganda</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="E238" t="inlineStr">
+      <c r="F238" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="E239" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>Uzbekistán</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="E240" t="inlineStr">
+      <c r="F240" t="inlineStr">
         <is>
           <t>Vanuatu</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="E241" t="inlineStr">
+      <c r="F241" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="E242" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>Vietnam</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="E243" t="inlineStr">
+      <c r="F243" t="inlineStr">
         <is>
           <t>Wallis y Futuna</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="E244" t="inlineStr">
+      <c r="F244" t="inlineStr">
         <is>
           <t>Yemen</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="E245" t="inlineStr">
+      <c r="F245" t="inlineStr">
         <is>
           <t>Yibuti</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="E246" t="inlineStr">
+      <c r="F246" t="inlineStr">
         <is>
           <t>Zambia</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="E247" t="inlineStr">
+      <c r="F247" t="inlineStr">
         <is>
           <t>Zimbabue</t>
         </is>

--- a/runac/demo/MPE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -239,7 +239,7 @@
 Nombre del dispositivo residencial específico de alojamiento. Debe coincidir con el registro oficial del archivo SCP.
 Qué se espera: texto
 Máximo 120 caracteres.
-Campo obligatorio.</t>
+No es obligatorio.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
@@ -969,9 +969,9 @@
           <t>Modalidad de cuidado</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Nombre de la residencia/hogar *</t>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Nombre de la residencia/hogar</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1289,16 +1289,16 @@
         <v>1</v>
       </c>
       <c r="AC4" s="5" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="AD4" s="5" t="n">
-        <v>45850</v>
+        <v>45851</v>
       </c>
       <c r="AE4" s="5" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="AF4" s="5" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="AG4" s="6" t="n">
         <v>76</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>45935</v>
+        <v>45936</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
         <v>2</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="AD5" s="5" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="AG5" s="6" t="n">
         <v>30</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1532,11 +1532,6 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Familia de acogimiento</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1645,16 +1640,16 @@
         <v>3</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="AD6" s="5" t="n">
-        <v>45956</v>
+        <v>45957</v>
       </c>
       <c r="AE6" s="5" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="AF6" s="5" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="AG6" s="6" t="n">
         <v>9</v>
@@ -1702,7 +1697,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1712,11 +1707,6 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1830,16 +1820,16 @@
         <v>4</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>45583</v>
+        <v>45584</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>45669</v>
+        <v>45670</v>
       </c>
       <c r="AG7" s="6" t="n">
         <v>9</v>
@@ -1887,7 +1877,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1897,11 +1887,6 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Familia de acogimiento</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2015,16 +2000,16 @@
         <v>5</v>
       </c>
       <c r="AC8" s="5" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="AD8" s="5" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="AE8" s="5" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>45948</v>
+        <v>45949</v>
       </c>
       <c r="AG8" s="6" t="n">
         <v>63</v>
@@ -2072,7 +2057,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2195,16 +2180,16 @@
         <v>6</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="AD9" s="5" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="AF9" s="5" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="AG9" s="6" t="n">
         <v>3</v>
@@ -2252,7 +2237,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2262,11 +2247,6 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2380,16 +2360,16 @@
         <v>7</v>
       </c>
       <c r="AC10" s="5" t="n">
-        <v>45605</v>
+        <v>45606</v>
       </c>
       <c r="AD10" s="5" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="AF10" s="5" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="AG10" s="6" t="n">
         <v>53</v>
@@ -2433,7 +2413,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2443,11 +2423,6 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2561,16 +2536,16 @@
         <v>8</v>
       </c>
       <c r="AC11" s="5" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="AD11" s="5" t="n">
-        <v>45787</v>
+        <v>45788</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="AF11" s="5" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="AG11" s="6" t="n">
         <v>8</v>
@@ -2614,7 +2589,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45602</v>
+        <v>45603</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2624,11 +2599,6 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>Otro</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2742,16 +2712,16 @@
         <v>9</v>
       </c>
       <c r="AC12" s="5" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="AD12" s="5" t="n">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="AE12" s="5" t="n">
-        <v>46392</v>
+        <v>46393</v>
       </c>
       <c r="AF12" s="5" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="AG12" s="6" t="n">
         <v>34</v>
@@ -2799,7 +2769,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45619</v>
+        <v>45620</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2809,11 +2779,6 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Familia de acogimiento</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2927,16 +2892,16 @@
         <v>10</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="AD13" s="5" t="n">
-        <v>45831</v>
+        <v>45832</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>45723</v>
+        <v>45724</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>45970</v>
+        <v>45971</v>
       </c>
       <c r="AG13" s="6" t="n">
         <v>79</v>
@@ -2980,7 +2945,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3103,16 +3068,16 @@
         <v>11</v>
       </c>
       <c r="AC14" s="5" t="n">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="AD14" s="5" t="n">
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="AE14" s="5" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="AF14" s="5" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="AG14" s="6" t="n">
         <v>71</v>
@@ -3156,7 +3121,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3166,11 +3131,6 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>Familia de acogimiento</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3279,16 +3239,16 @@
         <v>12</v>
       </c>
       <c r="AC15" s="5" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="AD15" s="5" t="n">
-        <v>45858</v>
+        <v>45859</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="AF15" s="5" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="AG15" s="6" t="n">
         <v>35</v>
@@ -3332,7 +3292,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45808</v>
+        <v>45809</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3342,11 +3302,6 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Familia de acogimiento</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3455,16 +3410,16 @@
         <v>13</v>
       </c>
       <c r="AC16" s="5" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="AD16" s="5" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="AF16" s="5" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="AG16" s="6" t="n">
         <v>77</v>
@@ -3508,7 +3463,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3518,11 +3473,6 @@
       <c r="C17" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3640,16 +3590,16 @@
         <v>14</v>
       </c>
       <c r="AC17" s="5" t="n">
-        <v>45597</v>
+        <v>45598</v>
       </c>
       <c r="AD17" s="5" t="n">
-        <v>45861</v>
+        <v>45862</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="AF17" s="5" t="n">
-        <v>45867</v>
+        <v>45868</v>
       </c>
       <c r="AG17" s="6" t="n">
         <v>90</v>
@@ -3697,7 +3647,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3707,11 +3657,6 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>Otro</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3825,16 +3770,16 @@
         <v>15</v>
       </c>
       <c r="AC18" s="5" t="n">
-        <v>46672</v>
+        <v>46673</v>
       </c>
       <c r="AD18" s="5" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="AE18" s="5" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="AF18" s="5" t="n">
-        <v>46542</v>
+        <v>46543</v>
       </c>
       <c r="AG18" s="6" t="n">
         <v>59</v>
@@ -3878,7 +3823,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4005,16 +3950,16 @@
         <v>16</v>
       </c>
       <c r="AC19" s="5" t="n">
-        <v>45843</v>
+        <v>45844</v>
       </c>
       <c r="AD19" s="5" t="n">
-        <v>45718</v>
+        <v>45719</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>45823</v>
+        <v>45824</v>
       </c>
       <c r="AF19" s="5" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="AG19" s="6" t="n">
         <v>96</v>
@@ -4058,7 +4003,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4068,11 +4013,6 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4181,16 +4121,16 @@
         <v>17</v>
       </c>
       <c r="AC20" s="5" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="AD20" s="5" t="n">
-        <v>45802</v>
+        <v>45803</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>45854</v>
+        <v>45855</v>
       </c>
       <c r="AF20" s="5" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="AG20" s="6" t="n">
         <v>27</v>
@@ -4234,7 +4174,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45728</v>
+        <v>45729</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4244,11 +4184,6 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4361,16 +4296,16 @@
         <v>18</v>
       </c>
       <c r="AC21" s="5" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="AD21" s="5" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="AF21" s="5" t="n">
-        <v>45841</v>
+        <v>45842</v>
       </c>
       <c r="AG21" s="6" t="n">
         <v>6666</v>
@@ -4414,7 +4349,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4537,16 +4472,16 @@
         <v>19</v>
       </c>
       <c r="AC22" s="5" t="n">
-        <v>46017</v>
+        <v>46018</v>
       </c>
       <c r="AD22" s="5" t="n">
-        <v>45902</v>
+        <v>45903</v>
       </c>
       <c r="AE22" s="5" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="AF22" s="5" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="AG22" s="6" t="n">
         <v>78</v>
@@ -4590,7 +4525,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4600,11 +4535,6 @@
       <c r="C23" t="inlineStr">
         <is>
           <t>Otro</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4713,16 +4643,16 @@
         <v>20</v>
       </c>
       <c r="AC23" s="5" t="n">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="AD23" s="5" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="AE23" s="5" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="AF23" s="5" t="n">
-        <v>45849</v>
+        <v>45850</v>
       </c>
       <c r="AG23" s="6" t="n">
         <v>63</v>
@@ -4766,7 +4696,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4776,11 +4706,6 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>Otro</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4893,16 +4818,16 @@
         <v>21</v>
       </c>
       <c r="AC24" s="5" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="AD24" s="5" t="n">
-        <v>46501</v>
+        <v>46502</v>
       </c>
       <c r="AE24" s="5" t="n">
-        <v>45779</v>
+        <v>45780</v>
       </c>
       <c r="AF24" s="5" t="n">
-        <v>45711</v>
+        <v>45712</v>
       </c>
       <c r="AG24" s="6" t="n">
         <v>98</v>
@@ -4946,7 +4871,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4956,11 +4881,6 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>Otro</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5078,16 +4998,16 @@
         <v>22</v>
       </c>
       <c r="AC25" s="5" t="n">
-        <v>45956</v>
+        <v>45957</v>
       </c>
       <c r="AD25" s="5" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="AE25" s="5" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="AF25" s="5" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="AG25" s="6" t="n">
         <v>25</v>
@@ -5135,7 +5055,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45990</v>
+        <v>45991</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5262,16 +5182,16 @@
         <v>23</v>
       </c>
       <c r="AC26" s="5" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="AD26" s="5" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="AE26" s="5" t="n">
-        <v>45828</v>
+        <v>45829</v>
       </c>
       <c r="AF26" s="5" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="AG26" s="6" t="n">
         <v>24</v>
@@ -5315,7 +5235,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5325,11 +5245,6 @@
       <c r="C27" t="inlineStr">
         <is>
           <t>Familia ampliada</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5443,16 +5358,16 @@
         <v>24</v>
       </c>
       <c r="AC27" s="5" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="AD27" s="5" t="n">
-        <v>46640</v>
+        <v>46641</v>
       </c>
       <c r="AE27" s="5" t="n">
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="AF27" s="5" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="AG27" s="6" t="n">
         <v>6666</v>
@@ -5500,7 +5415,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45815</v>
+        <v>45816</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5632,16 +5547,16 @@
         <v>25</v>
       </c>
       <c r="AC28" s="5" t="n">
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="AD28" s="5" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="AE28" s="5" t="n">
-        <v>45830</v>
+        <v>45831</v>
       </c>
       <c r="AF28" s="5" t="n">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="AG28" s="6" t="n">
         <v>60</v>
@@ -5685,7 +5600,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5817,16 +5732,16 @@
         <v>26</v>
       </c>
       <c r="AC29" s="5" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="AD29" s="5" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="AE29" s="5" t="n">
-        <v>45680</v>
+        <v>45681</v>
       </c>
       <c r="AF29" s="5" t="n">
-        <v>45833</v>
+        <v>45834</v>
       </c>
       <c r="AG29" s="6" t="n">
         <v>82</v>
@@ -5874,7 +5789,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5884,11 +5799,6 @@
       <c r="C30" t="inlineStr">
         <is>
           <t>Familia de acogimiento</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6002,16 +5912,16 @@
         <v>27</v>
       </c>
       <c r="AC30" s="5" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="AD30" s="5" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="AE30" s="5" t="n">
-        <v>45749</v>
+        <v>45750</v>
       </c>
       <c r="AF30" s="5" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="AG30" s="6" t="n">
         <v>9999</v>
@@ -6055,7 +5965,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -6065,11 +5975,6 @@
       <c r="C31" t="inlineStr">
         <is>
           <t>Familia de acogimiento</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6178,16 +6083,16 @@
         <v>28</v>
       </c>
       <c r="AC31" s="5" t="n">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="AD31" s="5" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="AE31" s="5" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="AF31" s="5" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="AG31" s="6" t="n">
         <v>25</v>
@@ -6235,7 +6140,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6367,16 +6272,16 @@
         <v>29</v>
       </c>
       <c r="AC32" s="5" t="n">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="AD32" s="5" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="AE32" s="5" t="n">
-        <v>46040</v>
+        <v>46041</v>
       </c>
       <c r="AF32" s="5" t="n">
-        <v>45859</v>
+        <v>45860</v>
       </c>
       <c r="AG32" s="6" t="n">
         <v>6</v>
@@ -6420,7 +6325,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46505</v>
+        <v>46506</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6430,11 +6335,6 @@
       <c r="C33" t="inlineStr">
         <is>
           <t>Otro</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6547,16 +6447,16 @@
         <v>30</v>
       </c>
       <c r="AC33" s="5" t="n">
-        <v>45725</v>
+        <v>45726</v>
       </c>
       <c r="AD33" s="5" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="AE33" s="5" t="n">
-        <v>45647</v>
+        <v>45648</v>
       </c>
       <c r="AF33" s="5" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="AG33" s="6" t="n">
         <v>31</v>
@@ -8633,8 +8533,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Nombre del dispositivo residencial específico de alojamiento. Debe coincidir con el registro oficial del archivo SCP.
-Campo obligatorio.</t>
+          <t>Nombre del dispositivo residencial específico de alojamiento. Debe coincidir con el registro oficial del archivo SCP.</t>
         </is>
       </c>
     </row>

--- a/runac/demo/MPE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPE_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -465,21 +465,23 @@
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Familia
-Qué se espera: una fecha, con formato dd/mm/aaaa
+Qué se espera: texto
+Máximo 120 caracteres.
 No es obligatorio.</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>ID familia ampliada
-Qué se espera: una fecha, con formato dd/mm/aaaa
+Qué se espera: un número entero
 No es obligatorio.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Familia Ampliada
-Qué se espera: una fecha, con formato dd/mm/aaaa
+Qué se espera: texto
+Máximo 120 caracteres.
 No es obligatorio.</t>
       </text>
     </comment>
@@ -1288,61 +1290,65 @@
       <c r="AB4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="AC4" s="5" t="n">
-        <v>45722</v>
-      </c>
-      <c r="AD4" s="5" t="n">
-        <v>45851</v>
-      </c>
-      <c r="AE4" s="5" t="n">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Familia Cabrera</t>
+        </is>
+      </c>
+      <c r="AD4" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Familia Romero</t>
+        </is>
+      </c>
+      <c r="AF4" s="5" t="n">
         <v>46055</v>
       </c>
-      <c r="AF4" s="5" t="n">
-        <v>45821</v>
-      </c>
       <c r="AG4" s="6" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso a la información</t>
+          <t>Ausencia de adulto responsable</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Dificultad en el acceso y sostenimiento de la seguridad social</t>
+          <t>Abandono</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>45936</v>
+        <v>46121</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1351,17 +1357,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1376,12 +1377,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1396,12 +1397,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Filipinas</t>
         </is>
       </c>
       <c r="O5" s="5" t="n">
@@ -1464,34 +1465,38 @@
       <c r="AB5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="AC5" s="5" t="n">
-        <v>46084</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>46209</v>
-      </c>
-      <c r="AE5" s="5" t="n">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Familia Martínez</t>
+        </is>
+      </c>
+      <c r="AD5" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="AF5" s="5" t="n">
         <v>46234</v>
       </c>
-      <c r="AF5" s="5" t="n">
-        <v>45603</v>
-      </c>
       <c r="AG5" s="6" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Búsqueda de origen</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Dificultades en el ejercicio de la responsabilidad parental</t>
+          <t>Negligencia</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1501,28 +1506,24 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 2</t>
-        </is>
-      </c>
+      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45901</v>
+        <v>46114</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1536,12 +1537,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>El Maitén</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1551,12 +1552,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1639,44 +1640,48 @@
       <c r="AB6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="AC6" s="5" t="n">
-        <v>46248</v>
-      </c>
-      <c r="AD6" s="5" t="n">
-        <v>45957</v>
-      </c>
-      <c r="AE6" s="5" t="n">
-        <v>45870</v>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Familia Paz</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
       </c>
       <c r="AF6" s="5" t="n">
-        <v>46006</v>
+        <v>46497</v>
       </c>
       <c r="AG6" s="6" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso a las prestaciones de salud por parte de los Organismos del Estado y la sociedad civil.</t>
+          <t>Explotación</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Restricción a la libertad de expresión</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1686,18 +1691,14 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 3</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>45811</v>
+        <v>45706</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1706,17 +1707,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1726,22 +1727,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Perdida de documentación</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>90000581</t>
+          <t>DNI en trámite</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1751,28 +1747,28 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="O7" s="5" t="n">
-        <v>41933</v>
+        <v>42200</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1792,17 +1788,17 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Publica</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1813,40 +1809,44 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="AC7" s="5" t="n">
-        <v>46117</v>
-      </c>
-      <c r="AD7" s="5" t="n">
-        <v>45584</v>
-      </c>
-      <c r="AE7" s="5" t="n">
-        <v>45848</v>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
+      </c>
+      <c r="AD7" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Familia Quiroga</t>
+        </is>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>45670</v>
+        <v>46023</v>
       </c>
       <c r="AG7" s="6" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Negligencia</t>
+          <t>Dificultades en el acceso a la inclusión y a las trayectorias educativas, juego y recreación por parte de los Organismos del Estado o de la sociedad civil.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Situación de calle</t>
+          <t>Dificultad en el acceso a la justicia</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1861,23 +1861,19 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 4</t>
-        </is>
-      </c>
+      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>46163</v>
+        <v>45835</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1886,7 +1882,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1896,7 +1892,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1906,22 +1902,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Posee N° doc. Extranjero</t>
+          <t>Perdida de documentación</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>90000685</t>
+          <t>90000707</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1936,61 +1932,65 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Territorios Australes y Antárticas Franceses</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="O8" s="5" t="n">
-        <v>41257</v>
+        <v>40614</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Secundaria completa</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 5</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>Sin datos</t>
@@ -1999,20 +1999,24 @@
       <c r="AB8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>45737</v>
-      </c>
-      <c r="AD8" s="5" t="n">
-        <v>46280</v>
-      </c>
-      <c r="AE8" s="5" t="n">
-        <v>45667</v>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
+      </c>
+      <c r="AD8" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Familia Sosa</t>
+        </is>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>45949</v>
+        <v>45780</v>
       </c>
       <c r="AG8" s="6" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2021,17 +2025,17 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Discriminación por género, creencia religiosas, ideología raza, nacionalidad, orientación sexual</t>
+          <t>Violencia institucional</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Trata y tráfico</t>
+          <t>Negligencia</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2046,14 +2050,10 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 5</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hogar convenido (sin declarar)</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Comodoro Rivadavia</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2091,17 +2091,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Quiroga</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Benjamín</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Perdida de documentación</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>90000843</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2111,102 +2116,110 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Liberia</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>42663</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Asiste</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Secundaria completa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Islas Georgias del Sur y Sandwich del Sur</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>41046</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Asiste</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Terciario/Universitario</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 6</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="AC9" s="5" t="n">
-        <v>46027</v>
-      </c>
-      <c r="AD9" s="5" t="n">
-        <v>46050</v>
-      </c>
-      <c r="AE9" s="5" t="n">
-        <v>46215</v>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Familia Díaz</t>
+        </is>
+      </c>
+      <c r="AD9" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Familia Díaz</t>
+        </is>
       </c>
       <c r="AF9" s="5" t="n">
-        <v>45934</v>
+        <v>46157</v>
       </c>
       <c r="AG9" s="6" t="n">
-        <v>3</v>
+        <v>3766</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso y en los tratamientos de salud (según autonomía progresiva y o adultos responsables)</t>
+          <t>Dificultades en la inclusión en trayectorias educativas, juego y recreación ( vinculado a los adultos responsables del cuidado o al propio NNyA según autonomía progresiva)</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Dificultades en el ejercicio de la responsabilidad parental</t>
+          <t>Abuso sexual infanto-juvenil</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2226,18 +2239,14 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 6</t>
-        </is>
-      </c>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>46220</v>
+        <v>45754</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2251,12 +2260,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Dolavon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2266,22 +2275,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Perdida de documentación</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>90000989</t>
+          <t>No posee N° DNI</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2291,97 +2295,101 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>42167</v>
+        <v>41174</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Terciario/Universitario</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="AC10" s="5" t="n">
-        <v>45606</v>
-      </c>
-      <c r="AD10" s="5" t="n">
-        <v>45839</v>
-      </c>
-      <c r="AE10" s="5" t="n">
-        <v>45918</v>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Familia Paz</t>
+        </is>
+      </c>
+      <c r="AD10" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
       </c>
       <c r="AF10" s="5" t="n">
-        <v>45847</v>
+        <v>45591</v>
       </c>
       <c r="AG10" s="6" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Accesibilidad a la justicia</t>
+          <t>Discriminación por género, creencia religiosas, ideología raza, nacionalidad, orientación sexual</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2391,29 +2399,29 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46169</v>
+        <v>46084</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2427,12 +2435,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Comodoro Rivadavia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2442,7 +2450,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2452,12 +2460,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Posee N° doc. Extranjero</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>90001119</t>
+          <t>DNI en trámite</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2467,19 +2470,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Islas Vírgenes Británicas</t>
+          <t>Territorio Británico del Océano Índico</t>
         </is>
       </c>
       <c r="O11" s="5" t="n">
-        <v>41202</v>
+        <v>40487</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2488,7 +2491,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Secundaria incompleta</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2498,24 +2501,24 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>Privada</t>
@@ -2523,7 +2526,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr"/>
@@ -2535,24 +2538,28 @@
       <c r="AB11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="AC11" s="5" t="n">
-        <v>45783</v>
-      </c>
-      <c r="AD11" s="5" t="n">
-        <v>45788</v>
-      </c>
-      <c r="AE11" s="5" t="n">
-        <v>46062</v>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Familia Martínez</t>
+        </is>
+      </c>
+      <c r="AD11" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
       </c>
       <c r="AF11" s="5" t="n">
-        <v>45870</v>
+        <v>46112</v>
       </c>
       <c r="AG11" s="6" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2562,7 +2569,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>Abandono</t>
+          <t>Explotación y trabajo infantil adolescente</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2582,14 +2589,18 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 8</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45603</v>
+        <v>46122</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2598,7 +2609,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2608,7 +2619,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2618,12 +2629,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2633,7 +2644,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>90001302</t>
+          <t>90001240</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2643,23 +2654,23 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Rusia</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="O12" s="5" t="n">
-        <v>41463</v>
+        <v>40413</v>
       </c>
       <c r="P12" s="6" t="n">
         <v>3</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2669,40 +2680,44 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 9</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -2711,39 +2726,43 @@
       <c r="AB12" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="AC12" s="5" t="n">
-        <v>45589</v>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>46040</v>
-      </c>
-      <c r="AE12" s="5" t="n">
-        <v>46393</v>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Familia Villalba</t>
+        </is>
+      </c>
+      <c r="AD12" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Familia Romero</t>
+        </is>
       </c>
       <c r="AF12" s="5" t="n">
-        <v>46285</v>
+        <v>46352</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso a la inclusión y a las trayectorias educativas, juego y recreación por parte de los Organismos del Estado o de la sociedad civil.</t>
+          <t>ASI ( abuso sexual a niñas niños y adolescentes)</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>Restricción a la libertad de expresión</t>
+          <t>Salud mental</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -2753,12 +2772,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2769,7 +2788,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>45620</v>
+        <v>45959</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2778,17 +2797,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Comodoro Rivadavia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2798,22 +2817,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Posee N° DNI</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>90001371</t>
+          <t>DNI en trámite</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2828,18 +2842,18 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Uzbekistán</t>
         </is>
       </c>
       <c r="O13" s="5" t="n">
-        <v>42485</v>
+        <v>40476</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2849,37 +2863,37 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Auditiva</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Publica</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr"/>
@@ -2891,39 +2905,43 @@
       <c r="AB13" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="5" t="n">
-        <v>46119</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>45832</v>
-      </c>
-      <c r="AE13" s="5" t="n">
-        <v>45724</v>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="AD13" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Familia Sosa</t>
+        </is>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>45971</v>
+        <v>45989</v>
       </c>
       <c r="AG13" s="6" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Trabajo infantil / trabajo adolescente</t>
+          <t>Dificultades en el acceso y en los tratamientos de salud (según autonomía progresiva y o adultos responsables)</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Abandono</t>
+          <t>Negligencia</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -2933,19 +2951,23 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr"/>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 10</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2954,22 +2976,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2979,17 +2996,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>No posee N° DNI</t>
+          <t>Perdida de documentación</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>90001526</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2999,19 +3021,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="O14" s="5" t="n">
-        <v>41260</v>
+        <v>42656</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3020,37 +3042,37 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Primaria incompleta</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3061,55 +3083,59 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB14" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="AC14" s="5" t="n">
-        <v>45628</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>46012</v>
-      </c>
-      <c r="AE14" s="5" t="n">
-        <v>46115</v>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Familia Romero</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
       </c>
       <c r="AF14" s="5" t="n">
-        <v>45828</v>
+        <v>46277</v>
       </c>
       <c r="AG14" s="6" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>ASI ( abuso sexual a niñas niños y adolescentes)</t>
+          <t>Dificultades en la inclusión en trayectorias educativas, juego y recreación ( vinculado a los adultos responsables del cuidado o al propio NNyA según autonomía progresiva)</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Explotación y trabajo infantil adolescente</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -3117,11 +3143,15 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 11</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46339</v>
+        <v>46620</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3130,17 +3160,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Ministerio de Desarrollo Social</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3150,17 +3180,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>90001649</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -3170,129 +3205,133 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>41201</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Asiste</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Primaria completa</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Bielorrusia</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>41627</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>No asiste</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Secundaria completa</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB15" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="AC15" s="5" t="n">
-        <v>45940</v>
-      </c>
-      <c r="AD15" s="5" t="n">
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Familia López</t>
+        </is>
+      </c>
+      <c r="AD15" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Familia Sosa</t>
+        </is>
+      </c>
+      <c r="AF15" s="5" t="n">
         <v>45859</v>
       </c>
-      <c r="AE15" s="5" t="n">
-        <v>45595</v>
-      </c>
-      <c r="AF15" s="5" t="n">
-        <v>46026</v>
-      </c>
       <c r="AG15" s="6" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Restricción a la libre asociación</t>
+          <t>Dificultades en el ejercicio de la responsabilidad parental</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Dificultad en el acceso a la justicia</t>
+          <t>Explotación y trabajo infantil adolescente</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AN15" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>45809</v>
+        <v>45799</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3301,17 +3340,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3321,17 +3360,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>No posee N° DNI</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>90001810</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -3341,19 +3385,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Gabón</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="O16" s="5" t="n">
-        <v>40463</v>
+        <v>40970</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -3367,12 +3411,12 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3387,17 +3431,17 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Privada</t>
+          <t>Publica</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr"/>
@@ -3409,39 +3453,43 @@
       <c r="AB16" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="AC16" s="5" t="n">
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="AD16" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Familia López</t>
+        </is>
+      </c>
+      <c r="AF16" s="5" t="n">
         <v>45686</v>
       </c>
-      <c r="AD16" s="5" t="n">
-        <v>46009</v>
-      </c>
-      <c r="AE16" s="5" t="n">
-        <v>46241</v>
-      </c>
-      <c r="AF16" s="5" t="n">
-        <v>46169</v>
-      </c>
       <c r="AG16" s="6" t="n">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Violencia institucional</t>
+          <t>Discriminación por género, creencia religiosas, ideología raza, nacionalidad, orientación sexual</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Restricción a la libertad de expresión</t>
+          <t>Vulneración a la identidad y discriminación</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -3451,19 +3499,23 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr"/>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 13</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>45690</v>
+        <v>45757</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3472,17 +3524,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Alojamiento formal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3492,7 +3549,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3502,12 +3559,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Perdida de documentación</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>90001986</t>
+          <t>Sin inscripción</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -3517,63 +3569,63 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>Lesoto</t>
         </is>
       </c>
       <c r="O17" s="5" t="n">
-        <v>40986</v>
+        <v>42384</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Nunca asistió</t>
+          <t>Primaria completa</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -3589,34 +3641,38 @@
       <c r="AB17" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="AC17" s="5" t="n">
-        <v>45598</v>
-      </c>
-      <c r="AD17" s="5" t="n">
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Familia Quiroga</t>
+        </is>
+      </c>
+      <c r="AD17" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Familia Villalba</t>
+        </is>
+      </c>
+      <c r="AF17" s="5" t="n">
         <v>45862</v>
       </c>
-      <c r="AE17" s="5" t="n">
-        <v>45946</v>
-      </c>
-      <c r="AF17" s="5" t="n">
-        <v>45868</v>
-      </c>
       <c r="AG17" s="6" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso y en los tratamientos de salud (según autonomía progresiva y o adultos responsables)</t>
+          <t>Restricción a la libre asociación</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Dificultad en el acceso a la vivienda y espacio saludable</t>
+          <t>Negligencia</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3626,28 +3682,24 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 14</t>
-        </is>
-      </c>
+      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>45972</v>
+        <v>45698</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3656,17 +3708,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3676,22 +3728,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Posee N° doc. Extranjero</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>90002129</t>
+          <t>DNI en trámite</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -3701,19 +3748,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Santa Elena</t>
         </is>
       </c>
       <c r="O18" s="5" t="n">
-        <v>41498</v>
+        <v>42554</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -3727,103 +3774,111 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB18" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="AC18" s="5" t="n">
-        <v>46673</v>
-      </c>
-      <c r="AD18" s="5" t="n">
-        <v>46050</v>
-      </c>
-      <c r="AE18" s="5" t="n">
-        <v>46077</v>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Familia Rodríguez</t>
+        </is>
+      </c>
+      <c r="AD18" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
       </c>
       <c r="AF18" s="5" t="n">
-        <v>46543</v>
+        <v>46040</v>
       </c>
       <c r="AG18" s="6" t="n">
-        <v>59</v>
+        <v>7777</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Encuentro espontáneo</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Dificultades en la inclusión en trayectorias educativas, juego y recreación ( vinculado a los adultos responsables del cuidado o al propio NNyA según autonomía progresiva)</t>
+          <t>Trata y Tráfico</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Dificultad en el acceso a la salud</t>
+          <t>Vulneración a la identidad y discriminación</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>45609</v>
+        <v>45871</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3832,22 +3887,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Hogar Los Álamos</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3857,17 +3907,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>90002205</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -3882,48 +3937,48 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="O19" s="5" t="n">
-        <v>42462</v>
+        <v>40899</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Secundaria incompleta</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Visceral</t>
+          <t>Motora</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3949,61 +4004,65 @@
       <c r="AB19" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="AC19" s="5" t="n">
-        <v>45844</v>
-      </c>
-      <c r="AD19" s="5" t="n">
-        <v>45719</v>
-      </c>
-      <c r="AE19" s="5" t="n">
-        <v>45824</v>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
+      </c>
+      <c r="AD19" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
       </c>
       <c r="AF19" s="5" t="n">
-        <v>46118</v>
+        <v>45827</v>
       </c>
       <c r="AG19" s="6" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Trata y Tráfico</t>
+          <t>Trabajo infantil / trabajo adolescente</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Explotación y trabajo infantil adolescente</t>
+          <t>Vulneración a la identidad y discriminación</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45639</v>
+        <v>46015</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4017,12 +4076,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Dolavon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4032,17 +4091,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>No posee N° DNI</t>
+          <t>DNI en trámite</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -4052,102 +4111,110 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="O20" s="5" t="n">
-        <v>42391</v>
+        <v>41349</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Primaria incompleta</t>
+          <t>Primaria completa</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="AB20" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="AC20" s="5" t="n">
-        <v>45725</v>
-      </c>
-      <c r="AD20" s="5" t="n">
-        <v>45803</v>
-      </c>
-      <c r="AE20" s="5" t="n">
-        <v>45855</v>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Familia Cabrera</t>
+        </is>
+      </c>
+      <c r="AD20" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
       </c>
       <c r="AF20" s="5" t="n">
-        <v>46217</v>
+        <v>45856</v>
       </c>
       <c r="AG20" s="6" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Negligencia</t>
+          <t>Dificultades en el acceso y en los tratamientos de salud (según autonomía progresiva y o adultos responsables)</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Abandono</t>
+          <t>Situación de calle</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4157,7 +4224,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -4174,7 +4241,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>45729</v>
+        <v>46295</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -4183,17 +4250,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Familia ampliada</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4203,22 +4270,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Posee N° DNI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>90002515</t>
+          <t>90002543</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -4228,108 +4295,113 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Jersey</t>
         </is>
       </c>
       <c r="O21" s="5" t="n">
-        <v>41835</v>
+        <v>41077</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>Secundaria incompleta</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 18</t>
-        </is>
-      </c>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB21" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="AC21" s="5" t="n">
-        <v>46253</v>
-      </c>
-      <c r="AD21" s="5" t="n">
-        <v>46195</v>
-      </c>
-      <c r="AE21" s="5" t="n">
-        <v>45622</v>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
+      </c>
+      <c r="AD21" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
       </c>
       <c r="AF21" s="5" t="n">
-        <v>45842</v>
+        <v>45877</v>
       </c>
       <c r="AG21" s="6" t="n">
-        <v>6666</v>
+        <v>3939</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
+          <t>Violencia</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Dificultad en el acceso a la salud</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>Violencia</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Autonomía</t>
-        </is>
-      </c>
       <c r="AL21" t="inlineStr">
         <is>
           <t>Sin datos</t>
@@ -4342,14 +4414,14 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46261</v>
+        <v>45849</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4358,22 +4430,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4383,17 +4450,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>Posee N° DNI</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>90002647</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -4408,14 +4480,14 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Yibuti</t>
+          <t>Niue</t>
         </is>
       </c>
       <c r="O22" s="5" t="n">
-        <v>41191</v>
+        <v>40460</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -4424,7 +4496,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Secundaria completa</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -4444,7 +4516,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -4465,30 +4537,34 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AB22" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="AC22" s="5" t="n">
-        <v>46018</v>
-      </c>
-      <c r="AD22" s="5" t="n">
-        <v>45903</v>
-      </c>
-      <c r="AE22" s="5" t="n">
-        <v>46109</v>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Familia Díaz</t>
+        </is>
+      </c>
+      <c r="AD22" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
       </c>
       <c r="AF22" s="5" t="n">
-        <v>45660</v>
+        <v>45703</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Policía</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -4498,22 +4574,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>Dificultad en el acceso a la justicia</t>
+          <t>Explotación y trabajo infantil adolescente</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -4521,11 +4597,15 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 19</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45961</v>
+        <v>46163</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4534,17 +4614,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4554,17 +4634,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>DNI en trámite</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4574,19 +4654,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Bielorrusia</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="O23" s="5" t="n">
-        <v>41414</v>
+        <v>41716</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -4595,7 +4675,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -4605,35 +4685,39 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 20</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Sin datos</t>
@@ -4642,61 +4726,65 @@
       <c r="AB23" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="AC23" s="5" t="n">
-        <v>45617</v>
-      </c>
-      <c r="AD23" s="5" t="n">
-        <v>45931</v>
-      </c>
-      <c r="AE23" s="5" t="n">
-        <v>46268</v>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
+      </c>
+      <c r="AD23" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
       </c>
       <c r="AF23" s="5" t="n">
-        <v>45850</v>
+        <v>45701</v>
       </c>
       <c r="AG23" s="6" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>ASI ( abuso sexual a niñas niños y adolescentes)</t>
+          <t>Dificultades en el acceso y en los tratamientos de salud (según autonomía progresiva y o adultos responsables)</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Trata y tráfico</t>
+          <t>Vulneración a la identidad y discriminación</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45650</v>
+        <v>45779</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4705,17 +4793,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Alojamiento formal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>El Maitén</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4725,17 +4818,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Benjamín</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Sin inscripción</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -4745,19 +4838,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="O24" s="5" t="n">
-        <v>40533</v>
+        <v>42316</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -4766,112 +4859,112 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Primaria incompleta</t>
+          <t>Secundaria completa</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 21</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
         </is>
       </c>
       <c r="AB24" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="AC24" s="5" t="n">
-        <v>45711</v>
-      </c>
-      <c r="AD24" s="5" t="n">
-        <v>46502</v>
-      </c>
-      <c r="AE24" s="5" t="n">
-        <v>45780</v>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Familia Díaz</t>
+        </is>
+      </c>
+      <c r="AD24" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
       </c>
       <c r="AF24" s="5" t="n">
-        <v>45712</v>
+        <v>45805</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Restricción a la libre asociación</t>
+          <t>Dificultades en el acceso a la inclusión y a las trayectorias educativas, juego y recreación por parte de los Organismos del Estado o de la sociedad civil.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Consumo problemático</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46054</v>
+        <v>45781</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4880,7 +4973,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4890,7 +4983,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4900,22 +4993,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Ledesma</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Posee N° doc. Extranjero</t>
+          <t>Perdida de documentación</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>90003084</t>
+          <t>90003103</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -4925,137 +5018,137 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Macao</t>
         </is>
       </c>
       <c r="O25" s="5" t="n">
-        <v>41921</v>
+        <v>40220</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Nunca asistió</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Publica</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Privada</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 22</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Sí</t>
         </is>
       </c>
       <c r="AB25" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="AC25" s="5" t="n">
-        <v>45957</v>
-      </c>
-      <c r="AD25" s="5" t="n">
-        <v>46158</v>
-      </c>
-      <c r="AE25" s="5" t="n">
-        <v>45732</v>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Familia Díaz</t>
+        </is>
+      </c>
+      <c r="AD25" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Familia Ojeda</t>
+        </is>
       </c>
       <c r="AF25" s="5" t="n">
-        <v>46091</v>
+        <v>46263</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Accesibilidad a la justicia</t>
+          <t>Dificultades en el ejercicio de la responsabilidad parental</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Consumo problemático</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Autonomía</t>
+          <t>Adopción</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 22</t>
-        </is>
-      </c>
+      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>45991</v>
+        <v>45796</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -5064,22 +5157,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>Rada Tilly</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -5094,12 +5182,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>DNI en trámite</t>
+          <t>Sin inscripción</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -5109,53 +5197,53 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Groenlandia</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>41208</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Asiste</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Terciario/Universitario</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Libia</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="n">
-        <v>40697</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Asiste</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Nunca asistió</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Auditiva</t>
-        </is>
-      </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -5181,39 +5269,43 @@
       <c r="AB26" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="AC26" s="5" t="n">
-        <v>45800</v>
-      </c>
-      <c r="AD26" s="5" t="n">
-        <v>45790</v>
-      </c>
-      <c r="AE26" s="5" t="n">
-        <v>45829</v>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Familia Rodríguez</t>
+        </is>
+      </c>
+      <c r="AD26" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
       </c>
       <c r="AF26" s="5" t="n">
-        <v>45932</v>
+        <v>45743</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Encuentro espontáneo</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Ausencia de adulto responsable</t>
+          <t>Discriminación por género, creencia religiosas, ideología raza, nacionalidad, orientación sexual</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>Consumo problemático</t>
+          <t>Dificultad en el acceso a la salud</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Autonomía</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -5228,14 +5320,14 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46226</v>
+        <v>45734</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -5249,12 +5341,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -5264,22 +5356,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Posee N° DNI</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>90003359</t>
+          <t>Sin inscripción</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -5289,19 +5376,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Moldavia</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="O27" s="5" t="n">
-        <v>42620</v>
+        <v>42189</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -5310,91 +5397,95 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>Secundaria completa</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Motora</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Sí</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>No</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB27" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="AC27" s="5" t="n">
-        <v>45645</v>
-      </c>
-      <c r="AD27" s="5" t="n">
-        <v>46641</v>
-      </c>
-      <c r="AE27" s="5" t="n">
-        <v>45604</v>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="AD27" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Familia Romero</t>
+        </is>
       </c>
       <c r="AF27" s="5" t="n">
-        <v>46197</v>
+        <v>45777</v>
       </c>
       <c r="AG27" s="6" t="n">
-        <v>6666</v>
+        <v>3946</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso y sostenimiento en la seguridad social</t>
+          <t>Discriminación por género, creencia religiosas, ideología raza, nacionalidad, orientación sexual</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Abuso sexual infanto-juvenil</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Adopción</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -5404,18 +5495,14 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 24</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>45816</v>
+        <v>45745</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5424,22 +5511,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Residencia El Ceibo</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5449,22 +5531,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Perdida de documentación</t>
+          <t>Posee N° doc. Extranjero</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>90003509</t>
+          <t>90003464</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -5474,19 +5556,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Islas Georgias del Sur y Sandwich del Sur</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="O28" s="5" t="n">
-        <v>40649</v>
+        <v>40425</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -5495,7 +5577,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Terciario/Universitario</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -5505,7 +5587,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -5515,7 +5597,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -5530,14 +5612,10 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 25</t>
-        </is>
-      </c>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>Sin datos</t>
@@ -5546,20 +5624,24 @@
       <c r="AB28" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="AC28" s="5" t="n">
-        <v>45698</v>
-      </c>
-      <c r="AD28" s="5" t="n">
-        <v>45985</v>
-      </c>
-      <c r="AE28" s="5" t="n">
-        <v>45831</v>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Familia Fernández</t>
+        </is>
+      </c>
+      <c r="AD28" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Familia Gómez</t>
+        </is>
       </c>
       <c r="AF28" s="5" t="n">
-        <v>46153</v>
+        <v>45862</v>
       </c>
       <c r="AG28" s="6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5568,12 +5650,12 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso y sostenimiento en la seguridad social</t>
+          <t>Dificultades en el acceso a la vivienda y/o a condiciones saludables del medio ambiente</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Violencia</t>
+          <t>Consumo problemático</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5583,12 +5665,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
@@ -5596,11 +5678,15 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 25</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46198</v>
+        <v>45991</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -5609,12 +5695,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5624,7 +5705,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -5634,22 +5715,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Ledesma</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Posee N° DNI</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>90003573</t>
+          <t>90003642</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -5659,19 +5740,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Pakistán</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="O29" s="5" t="n">
-        <v>42535</v>
+        <v>40989</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -5680,49 +5761,45 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Secundaria completa</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 26</t>
-        </is>
-      </c>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>No</t>
@@ -5731,20 +5808,24 @@
       <c r="AB29" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="AC29" s="5" t="n">
-        <v>45996</v>
-      </c>
-      <c r="AD29" s="5" t="n">
-        <v>46095</v>
-      </c>
-      <c r="AE29" s="5" t="n">
-        <v>45681</v>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
+      </c>
+      <c r="AD29" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Familia Paz</t>
+        </is>
       </c>
       <c r="AF29" s="5" t="n">
-        <v>45834</v>
+        <v>45698</v>
       </c>
       <c r="AG29" s="6" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5753,12 +5834,12 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Búsqueda de origen</t>
+          <t>Discriminación por género, creencia religiosas, ideología raza, nacionalidad, orientación sexual</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>Consumo problemático</t>
+          <t>Situación de calle</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -5768,7 +5849,7 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -5789,7 +5870,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>46116</v>
+        <v>46198</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -5798,7 +5879,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Alojamiento formal</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5808,7 +5894,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5818,22 +5904,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Rodríguez</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Posee N° doc. Extranjero</t>
+          <t>Posee N° DNI</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>90003769</t>
+          <t>90003710</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -5848,61 +5934,65 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Islas Turcas y Caicos</t>
+          <t>Pakistán</t>
         </is>
       </c>
       <c r="O30" s="5" t="n">
-        <v>40539</v>
+        <v>42535</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Publica</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 27</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>No</t>
@@ -5911,44 +6001,48 @@
       <c r="AB30" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="AC30" s="5" t="n">
-        <v>46225</v>
-      </c>
-      <c r="AD30" s="5" t="n">
-        <v>46088</v>
-      </c>
-      <c r="AE30" s="5" t="n">
-        <v>45750</v>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Familia Rodríguez</t>
+        </is>
+      </c>
+      <c r="AD30" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Familia Ledesma</t>
+        </is>
       </c>
       <c r="AF30" s="5" t="n">
-        <v>45910</v>
+        <v>45834</v>
       </c>
       <c r="AG30" s="6" t="n">
-        <v>9999</v>
+        <v>4067</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Policía</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Restricción a la libre asociación</t>
+          <t>Violencia</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>Consumo problemático</t>
+          <t>Vulneración a la identidad y discriminación</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Reintegro familiar</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -5958,14 +6052,18 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr"/>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 27</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46118</v>
+        <v>46243</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -5974,17 +6072,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Familia de acogimiento</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5994,7 +6092,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -6004,7 +6102,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>No posee N° DNI</t>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>90003887</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -6014,23 +6117,23 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Sri lanka</t>
         </is>
       </c>
       <c r="O31" s="5" t="n">
-        <v>40660</v>
+        <v>40183</v>
       </c>
       <c r="P31" s="6" t="n">
         <v>13</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Asiste</t>
+          <t>No asiste</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -6040,32 +6143,32 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Publica</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -6082,34 +6185,38 @@
       <c r="AB31" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="AC31" s="5" t="n">
-        <v>45813</v>
-      </c>
-      <c r="AD31" s="5" t="n">
-        <v>45716</v>
-      </c>
-      <c r="AE31" s="5" t="n">
-        <v>46132</v>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Familia Rodríguez</t>
+        </is>
+      </c>
+      <c r="AD31" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Familia López</t>
+        </is>
       </c>
       <c r="AF31" s="5" t="n">
-        <v>45888</v>
+        <v>45986</v>
       </c>
       <c r="AG31" s="6" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Juzgado</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Trabajo infantil / trabajo adolescente</t>
+          <t>Explotación</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>Dificultad en el acceso a la vivienda y espacio saludable</t>
+          <t>Dificultad en el acceso a la justicia</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6119,17 +6226,17 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -6140,7 +6247,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>46007</v>
+        <v>46118</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -6149,22 +6256,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alojamiento formal</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Centro Municipal Norte</t>
+          <t>Familia de acogimiento</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Esquel</t>
+          <t>Rada Tilly</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -6174,22 +6276,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Luis</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Perdida de documentación</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>90004057</t>
+          <t>No posee N° DNI</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -6204,65 +6301,61 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Taiwán</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="O32" s="5" t="n">
-        <v>40787</v>
+        <v>40660</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Primaria completa</t>
+          <t>Secundaria incompleta</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 29</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -6271,39 +6364,43 @@
       <c r="AB32" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="AC32" s="5" t="n">
-        <v>45695</v>
-      </c>
-      <c r="AD32" s="5" t="n">
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Familia Díaz</t>
+        </is>
+      </c>
+      <c r="AD32" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Familia López</t>
+        </is>
+      </c>
+      <c r="AF32" s="5" t="n">
         <v>45888</v>
       </c>
-      <c r="AE32" s="5" t="n">
-        <v>46041</v>
-      </c>
-      <c r="AF32" s="5" t="n">
-        <v>45860</v>
-      </c>
       <c r="AG32" s="6" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Juzgado</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Accesibilidad a la justicia</t>
+          <t>Trabajo infantil / trabajo adolescente</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>Consumo problemático</t>
+          <t>Dificultad en el acceso a la vivienda y espacio saludable</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Reintegro familiar</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -6313,19 +6410,23 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr"/>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 29</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46506</v>
+        <v>46292</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -6334,17 +6435,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Familia ampliada</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Comodoro Rivadavia</t>
+          <t>Dolavon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -6354,17 +6455,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Sin inscripción</t>
+          <t>Perdida de documentación</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>90004179</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -6374,23 +6480,23 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Islas Turcas y Caicos</t>
         </is>
       </c>
       <c r="O33" s="5" t="n">
-        <v>41264</v>
+        <v>41497</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>No asiste</t>
+          <t>Asiste</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -6405,32 +6511,32 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Privada</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -6446,34 +6552,38 @@
       <c r="AB33" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="AC33" s="5" t="n">
-        <v>45726</v>
-      </c>
-      <c r="AD33" s="5" t="n">
-        <v>46244</v>
-      </c>
-      <c r="AE33" s="5" t="n">
-        <v>45648</v>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Familia Cabrera</t>
+        </is>
+      </c>
+      <c r="AD33" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Familia Romero</t>
+        </is>
       </c>
       <c r="AF33" s="5" t="n">
-        <v>46210</v>
+        <v>45601</v>
       </c>
       <c r="AG33" s="6" t="n">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Dificultades en el acceso a la inclusión y a las trayectorias educativas, juego y recreación por parte de los Organismos del Estado o de la sociedad civil.</t>
+          <t>Explotación</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>Negligencia</t>
+          <t>Abuso sexual infanto-juvenil</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6488,7 +6598,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -6503,9 +6613,7 @@
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="6" t="n"/>
       <c r="AB34" s="6" t="n"/>
-      <c r="AC34" s="5" t="n"/>
-      <c r="AD34" s="5" t="n"/>
-      <c r="AE34" s="5" t="n"/>
+      <c r="AD34" s="6" t="n"/>
       <c r="AF34" s="5" t="n"/>
       <c r="AG34" s="6" t="n"/>
     </row>
@@ -6514,9 +6622,7 @@
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="6" t="n"/>
       <c r="AB35" s="6" t="n"/>
-      <c r="AC35" s="5" t="n"/>
-      <c r="AD35" s="5" t="n"/>
-      <c r="AE35" s="5" t="n"/>
+      <c r="AD35" s="6" t="n"/>
       <c r="AF35" s="5" t="n"/>
       <c r="AG35" s="6" t="n"/>
     </row>
@@ -6525,9 +6631,7 @@
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="6" t="n"/>
       <c r="AB36" s="6" t="n"/>
-      <c r="AC36" s="5" t="n"/>
-      <c r="AD36" s="5" t="n"/>
-      <c r="AE36" s="5" t="n"/>
+      <c r="AD36" s="6" t="n"/>
       <c r="AF36" s="5" t="n"/>
       <c r="AG36" s="6" t="n"/>
     </row>
@@ -6536,9 +6640,7 @@
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="6" t="n"/>
       <c r="AB37" s="6" t="n"/>
-      <c r="AC37" s="5" t="n"/>
-      <c r="AD37" s="5" t="n"/>
-      <c r="AE37" s="5" t="n"/>
+      <c r="AD37" s="6" t="n"/>
       <c r="AF37" s="5" t="n"/>
       <c r="AG37" s="6" t="n"/>
     </row>
@@ -6547,9 +6649,7 @@
       <c r="O38" s="5" t="n"/>
       <c r="P38" s="6" t="n"/>
       <c r="AB38" s="6" t="n"/>
-      <c r="AC38" s="5" t="n"/>
-      <c r="AD38" s="5" t="n"/>
-      <c r="AE38" s="5" t="n"/>
+      <c r="AD38" s="6" t="n"/>
       <c r="AF38" s="5" t="n"/>
       <c r="AG38" s="6" t="n"/>
     </row>
@@ -6558,9 +6658,7 @@
       <c r="O39" s="5" t="n"/>
       <c r="P39" s="6" t="n"/>
       <c r="AB39" s="6" t="n"/>
-      <c r="AC39" s="5" t="n"/>
-      <c r="AD39" s="5" t="n"/>
-      <c r="AE39" s="5" t="n"/>
+      <c r="AD39" s="6" t="n"/>
       <c r="AF39" s="5" t="n"/>
       <c r="AG39" s="6" t="n"/>
     </row>
@@ -6569,9 +6667,7 @@
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="6" t="n"/>
       <c r="AB40" s="6" t="n"/>
-      <c r="AC40" s="5" t="n"/>
-      <c r="AD40" s="5" t="n"/>
-      <c r="AE40" s="5" t="n"/>
+      <c r="AD40" s="6" t="n"/>
       <c r="AF40" s="5" t="n"/>
       <c r="AG40" s="6" t="n"/>
     </row>
@@ -6580,9 +6676,7 @@
       <c r="O41" s="5" t="n"/>
       <c r="P41" s="6" t="n"/>
       <c r="AB41" s="6" t="n"/>
-      <c r="AC41" s="5" t="n"/>
-      <c r="AD41" s="5" t="n"/>
-      <c r="AE41" s="5" t="n"/>
+      <c r="AD41" s="6" t="n"/>
       <c r="AF41" s="5" t="n"/>
       <c r="AG41" s="6" t="n"/>
     </row>
@@ -6591,9 +6685,7 @@
       <c r="O42" s="5" t="n"/>
       <c r="P42" s="6" t="n"/>
       <c r="AB42" s="6" t="n"/>
-      <c r="AC42" s="5" t="n"/>
-      <c r="AD42" s="5" t="n"/>
-      <c r="AE42" s="5" t="n"/>
+      <c r="AD42" s="6" t="n"/>
       <c r="AF42" s="5" t="n"/>
       <c r="AG42" s="6" t="n"/>
     </row>
@@ -6602,9 +6694,7 @@
       <c r="O43" s="5" t="n"/>
       <c r="P43" s="6" t="n"/>
       <c r="AB43" s="6" t="n"/>
-      <c r="AC43" s="5" t="n"/>
-      <c r="AD43" s="5" t="n"/>
-      <c r="AE43" s="5" t="n"/>
+      <c r="AD43" s="6" t="n"/>
       <c r="AF43" s="5" t="n"/>
       <c r="AG43" s="6" t="n"/>
     </row>
@@ -6613,9 +6703,7 @@
       <c r="O44" s="5" t="n"/>
       <c r="P44" s="6" t="n"/>
       <c r="AB44" s="6" t="n"/>
-      <c r="AC44" s="5" t="n"/>
-      <c r="AD44" s="5" t="n"/>
-      <c r="AE44" s="5" t="n"/>
+      <c r="AD44" s="6" t="n"/>
       <c r="AF44" s="5" t="n"/>
       <c r="AG44" s="6" t="n"/>
     </row>
@@ -6624,9 +6712,7 @@
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="6" t="n"/>
       <c r="AB45" s="6" t="n"/>
-      <c r="AC45" s="5" t="n"/>
-      <c r="AD45" s="5" t="n"/>
-      <c r="AE45" s="5" t="n"/>
+      <c r="AD45" s="6" t="n"/>
       <c r="AF45" s="5" t="n"/>
       <c r="AG45" s="6" t="n"/>
     </row>
@@ -6635,9 +6721,7 @@
       <c r="O46" s="5" t="n"/>
       <c r="P46" s="6" t="n"/>
       <c r="AB46" s="6" t="n"/>
-      <c r="AC46" s="5" t="n"/>
-      <c r="AD46" s="5" t="n"/>
-      <c r="AE46" s="5" t="n"/>
+      <c r="AD46" s="6" t="n"/>
       <c r="AF46" s="5" t="n"/>
       <c r="AG46" s="6" t="n"/>
     </row>
@@ -6646,9 +6730,7 @@
       <c r="O47" s="5" t="n"/>
       <c r="P47" s="6" t="n"/>
       <c r="AB47" s="6" t="n"/>
-      <c r="AC47" s="5" t="n"/>
-      <c r="AD47" s="5" t="n"/>
-      <c r="AE47" s="5" t="n"/>
+      <c r="AD47" s="6" t="n"/>
       <c r="AF47" s="5" t="n"/>
       <c r="AG47" s="6" t="n"/>
     </row>
@@ -6657,9 +6739,7 @@
       <c r="O48" s="5" t="n"/>
       <c r="P48" s="6" t="n"/>
       <c r="AB48" s="6" t="n"/>
-      <c r="AC48" s="5" t="n"/>
-      <c r="AD48" s="5" t="n"/>
-      <c r="AE48" s="5" t="n"/>
+      <c r="AD48" s="6" t="n"/>
       <c r="AF48" s="5" t="n"/>
       <c r="AG48" s="6" t="n"/>
     </row>
@@ -6668,9 +6748,7 @@
       <c r="O49" s="5" t="n"/>
       <c r="P49" s="6" t="n"/>
       <c r="AB49" s="6" t="n"/>
-      <c r="AC49" s="5" t="n"/>
-      <c r="AD49" s="5" t="n"/>
-      <c r="AE49" s="5" t="n"/>
+      <c r="AD49" s="6" t="n"/>
       <c r="AF49" s="5" t="n"/>
       <c r="AG49" s="6" t="n"/>
     </row>
@@ -6679,9 +6757,7 @@
       <c r="O50" s="5" t="n"/>
       <c r="P50" s="6" t="n"/>
       <c r="AB50" s="6" t="n"/>
-      <c r="AC50" s="5" t="n"/>
-      <c r="AD50" s="5" t="n"/>
-      <c r="AE50" s="5" t="n"/>
+      <c r="AD50" s="6" t="n"/>
       <c r="AF50" s="5" t="n"/>
       <c r="AG50" s="6" t="n"/>
     </row>
@@ -6690,9 +6766,7 @@
       <c r="O51" s="5" t="n"/>
       <c r="P51" s="6" t="n"/>
       <c r="AB51" s="6" t="n"/>
-      <c r="AC51" s="5" t="n"/>
-      <c r="AD51" s="5" t="n"/>
-      <c r="AE51" s="5" t="n"/>
+      <c r="AD51" s="6" t="n"/>
       <c r="AF51" s="5" t="n"/>
       <c r="AG51" s="6" t="n"/>
     </row>
@@ -6701,9 +6775,7 @@
       <c r="O52" s="5" t="n"/>
       <c r="P52" s="6" t="n"/>
       <c r="AB52" s="6" t="n"/>
-      <c r="AC52" s="5" t="n"/>
-      <c r="AD52" s="5" t="n"/>
-      <c r="AE52" s="5" t="n"/>
+      <c r="AD52" s="6" t="n"/>
       <c r="AF52" s="5" t="n"/>
       <c r="AG52" s="6" t="n"/>
     </row>
@@ -6712,9 +6784,7 @@
       <c r="O53" s="5" t="n"/>
       <c r="P53" s="6" t="n"/>
       <c r="AB53" s="6" t="n"/>
-      <c r="AC53" s="5" t="n"/>
-      <c r="AD53" s="5" t="n"/>
-      <c r="AE53" s="5" t="n"/>
+      <c r="AD53" s="6" t="n"/>
       <c r="AF53" s="5" t="n"/>
       <c r="AG53" s="6" t="n"/>
     </row>
@@ -6723,9 +6793,7 @@
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="6" t="n"/>
       <c r="AB54" s="6" t="n"/>
-      <c r="AC54" s="5" t="n"/>
-      <c r="AD54" s="5" t="n"/>
-      <c r="AE54" s="5" t="n"/>
+      <c r="AD54" s="6" t="n"/>
       <c r="AF54" s="5" t="n"/>
       <c r="AG54" s="6" t="n"/>
     </row>
@@ -6734,9 +6802,7 @@
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="6" t="n"/>
       <c r="AB55" s="6" t="n"/>
-      <c r="AC55" s="5" t="n"/>
-      <c r="AD55" s="5" t="n"/>
-      <c r="AE55" s="5" t="n"/>
+      <c r="AD55" s="6" t="n"/>
       <c r="AF55" s="5" t="n"/>
       <c r="AG55" s="6" t="n"/>
     </row>
@@ -6745,9 +6811,7 @@
       <c r="O56" s="5" t="n"/>
       <c r="P56" s="6" t="n"/>
       <c r="AB56" s="6" t="n"/>
-      <c r="AC56" s="5" t="n"/>
-      <c r="AD56" s="5" t="n"/>
-      <c r="AE56" s="5" t="n"/>
+      <c r="AD56" s="6" t="n"/>
       <c r="AF56" s="5" t="n"/>
       <c r="AG56" s="6" t="n"/>
     </row>
@@ -6756,9 +6820,7 @@
       <c r="O57" s="5" t="n"/>
       <c r="P57" s="6" t="n"/>
       <c r="AB57" s="6" t="n"/>
-      <c r="AC57" s="5" t="n"/>
-      <c r="AD57" s="5" t="n"/>
-      <c r="AE57" s="5" t="n"/>
+      <c r="AD57" s="6" t="n"/>
       <c r="AF57" s="5" t="n"/>
       <c r="AG57" s="6" t="n"/>
     </row>
@@ -6767,9 +6829,7 @@
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="6" t="n"/>
       <c r="AB58" s="6" t="n"/>
-      <c r="AC58" s="5" t="n"/>
-      <c r="AD58" s="5" t="n"/>
-      <c r="AE58" s="5" t="n"/>
+      <c r="AD58" s="6" t="n"/>
       <c r="AF58" s="5" t="n"/>
       <c r="AG58" s="6" t="n"/>
     </row>
@@ -6778,9 +6838,7 @@
       <c r="O59" s="5" t="n"/>
       <c r="P59" s="6" t="n"/>
       <c r="AB59" s="6" t="n"/>
-      <c r="AC59" s="5" t="n"/>
-      <c r="AD59" s="5" t="n"/>
-      <c r="AE59" s="5" t="n"/>
+      <c r="AD59" s="6" t="n"/>
       <c r="AF59" s="5" t="n"/>
       <c r="AG59" s="6" t="n"/>
     </row>
@@ -6789,9 +6847,7 @@
       <c r="O60" s="5" t="n"/>
       <c r="P60" s="6" t="n"/>
       <c r="AB60" s="6" t="n"/>
-      <c r="AC60" s="5" t="n"/>
-      <c r="AD60" s="5" t="n"/>
-      <c r="AE60" s="5" t="n"/>
+      <c r="AD60" s="6" t="n"/>
       <c r="AF60" s="5" t="n"/>
       <c r="AG60" s="6" t="n"/>
     </row>
@@ -6800,9 +6856,7 @@
       <c r="O61" s="5" t="n"/>
       <c r="P61" s="6" t="n"/>
       <c r="AB61" s="6" t="n"/>
-      <c r="AC61" s="5" t="n"/>
-      <c r="AD61" s="5" t="n"/>
-      <c r="AE61" s="5" t="n"/>
+      <c r="AD61" s="6" t="n"/>
       <c r="AF61" s="5" t="n"/>
       <c r="AG61" s="6" t="n"/>
     </row>
@@ -6811,9 +6865,7 @@
       <c r="O62" s="5" t="n"/>
       <c r="P62" s="6" t="n"/>
       <c r="AB62" s="6" t="n"/>
-      <c r="AC62" s="5" t="n"/>
-      <c r="AD62" s="5" t="n"/>
-      <c r="AE62" s="5" t="n"/>
+      <c r="AD62" s="6" t="n"/>
       <c r="AF62" s="5" t="n"/>
       <c r="AG62" s="6" t="n"/>
     </row>
@@ -6822,9 +6874,7 @@
       <c r="O63" s="5" t="n"/>
       <c r="P63" s="6" t="n"/>
       <c r="AB63" s="6" t="n"/>
-      <c r="AC63" s="5" t="n"/>
-      <c r="AD63" s="5" t="n"/>
-      <c r="AE63" s="5" t="n"/>
+      <c r="AD63" s="6" t="n"/>
       <c r="AF63" s="5" t="n"/>
       <c r="AG63" s="6" t="n"/>
     </row>
@@ -6833,9 +6883,7 @@
       <c r="O64" s="5" t="n"/>
       <c r="P64" s="6" t="n"/>
       <c r="AB64" s="6" t="n"/>
-      <c r="AC64" s="5" t="n"/>
-      <c r="AD64" s="5" t="n"/>
-      <c r="AE64" s="5" t="n"/>
+      <c r="AD64" s="6" t="n"/>
       <c r="AF64" s="5" t="n"/>
       <c r="AG64" s="6" t="n"/>
     </row>
@@ -6844,9 +6892,7 @@
       <c r="O65" s="5" t="n"/>
       <c r="P65" s="6" t="n"/>
       <c r="AB65" s="6" t="n"/>
-      <c r="AC65" s="5" t="n"/>
-      <c r="AD65" s="5" t="n"/>
-      <c r="AE65" s="5" t="n"/>
+      <c r="AD65" s="6" t="n"/>
       <c r="AF65" s="5" t="n"/>
       <c r="AG65" s="6" t="n"/>
     </row>
@@ -6855,9 +6901,7 @@
       <c r="O66" s="5" t="n"/>
       <c r="P66" s="6" t="n"/>
       <c r="AB66" s="6" t="n"/>
-      <c r="AC66" s="5" t="n"/>
-      <c r="AD66" s="5" t="n"/>
-      <c r="AE66" s="5" t="n"/>
+      <c r="AD66" s="6" t="n"/>
       <c r="AF66" s="5" t="n"/>
       <c r="AG66" s="6" t="n"/>
     </row>
@@ -6866,9 +6910,7 @@
       <c r="O67" s="5" t="n"/>
       <c r="P67" s="6" t="n"/>
       <c r="AB67" s="6" t="n"/>
-      <c r="AC67" s="5" t="n"/>
-      <c r="AD67" s="5" t="n"/>
-      <c r="AE67" s="5" t="n"/>
+      <c r="AD67" s="6" t="n"/>
       <c r="AF67" s="5" t="n"/>
       <c r="AG67" s="6" t="n"/>
     </row>
@@ -6877,9 +6919,7 @@
       <c r="O68" s="5" t="n"/>
       <c r="P68" s="6" t="n"/>
       <c r="AB68" s="6" t="n"/>
-      <c r="AC68" s="5" t="n"/>
-      <c r="AD68" s="5" t="n"/>
-      <c r="AE68" s="5" t="n"/>
+      <c r="AD68" s="6" t="n"/>
       <c r="AF68" s="5" t="n"/>
       <c r="AG68" s="6" t="n"/>
     </row>
@@ -6888,9 +6928,7 @@
       <c r="O69" s="5" t="n"/>
       <c r="P69" s="6" t="n"/>
       <c r="AB69" s="6" t="n"/>
-      <c r="AC69" s="5" t="n"/>
-      <c r="AD69" s="5" t="n"/>
-      <c r="AE69" s="5" t="n"/>
+      <c r="AD69" s="6" t="n"/>
       <c r="AF69" s="5" t="n"/>
       <c r="AG69" s="6" t="n"/>
     </row>
@@ -6899,9 +6937,7 @@
       <c r="O70" s="5" t="n"/>
       <c r="P70" s="6" t="n"/>
       <c r="AB70" s="6" t="n"/>
-      <c r="AC70" s="5" t="n"/>
-      <c r="AD70" s="5" t="n"/>
-      <c r="AE70" s="5" t="n"/>
+      <c r="AD70" s="6" t="n"/>
       <c r="AF70" s="5" t="n"/>
       <c r="AG70" s="6" t="n"/>
     </row>
@@ -6910,9 +6946,7 @@
       <c r="O71" s="5" t="n"/>
       <c r="P71" s="6" t="n"/>
       <c r="AB71" s="6" t="n"/>
-      <c r="AC71" s="5" t="n"/>
-      <c r="AD71" s="5" t="n"/>
-      <c r="AE71" s="5" t="n"/>
+      <c r="AD71" s="6" t="n"/>
       <c r="AF71" s="5" t="n"/>
       <c r="AG71" s="6" t="n"/>
     </row>
@@ -6921,9 +6955,7 @@
       <c r="O72" s="5" t="n"/>
       <c r="P72" s="6" t="n"/>
       <c r="AB72" s="6" t="n"/>
-      <c r="AC72" s="5" t="n"/>
-      <c r="AD72" s="5" t="n"/>
-      <c r="AE72" s="5" t="n"/>
+      <c r="AD72" s="6" t="n"/>
       <c r="AF72" s="5" t="n"/>
       <c r="AG72" s="6" t="n"/>
     </row>
@@ -6932,9 +6964,7 @@
       <c r="O73" s="5" t="n"/>
       <c r="P73" s="6" t="n"/>
       <c r="AB73" s="6" t="n"/>
-      <c r="AC73" s="5" t="n"/>
-      <c r="AD73" s="5" t="n"/>
-      <c r="AE73" s="5" t="n"/>
+      <c r="AD73" s="6" t="n"/>
       <c r="AF73" s="5" t="n"/>
       <c r="AG73" s="6" t="n"/>
     </row>
@@ -6943,9 +6973,7 @@
       <c r="O74" s="5" t="n"/>
       <c r="P74" s="6" t="n"/>
       <c r="AB74" s="6" t="n"/>
-      <c r="AC74" s="5" t="n"/>
-      <c r="AD74" s="5" t="n"/>
-      <c r="AE74" s="5" t="n"/>
+      <c r="AD74" s="6" t="n"/>
       <c r="AF74" s="5" t="n"/>
       <c r="AG74" s="6" t="n"/>
     </row>
@@ -6954,9 +6982,7 @@
       <c r="O75" s="5" t="n"/>
       <c r="P75" s="6" t="n"/>
       <c r="AB75" s="6" t="n"/>
-      <c r="AC75" s="5" t="n"/>
-      <c r="AD75" s="5" t="n"/>
-      <c r="AE75" s="5" t="n"/>
+      <c r="AD75" s="6" t="n"/>
       <c r="AF75" s="5" t="n"/>
       <c r="AG75" s="6" t="n"/>
     </row>
@@ -6965,9 +6991,7 @@
       <c r="O76" s="5" t="n"/>
       <c r="P76" s="6" t="n"/>
       <c r="AB76" s="6" t="n"/>
-      <c r="AC76" s="5" t="n"/>
-      <c r="AD76" s="5" t="n"/>
-      <c r="AE76" s="5" t="n"/>
+      <c r="AD76" s="6" t="n"/>
       <c r="AF76" s="5" t="n"/>
       <c r="AG76" s="6" t="n"/>
     </row>
@@ -6976,9 +7000,7 @@
       <c r="O77" s="5" t="n"/>
       <c r="P77" s="6" t="n"/>
       <c r="AB77" s="6" t="n"/>
-      <c r="AC77" s="5" t="n"/>
-      <c r="AD77" s="5" t="n"/>
-      <c r="AE77" s="5" t="n"/>
+      <c r="AD77" s="6" t="n"/>
       <c r="AF77" s="5" t="n"/>
       <c r="AG77" s="6" t="n"/>
     </row>
@@ -6987,9 +7009,7 @@
       <c r="O78" s="5" t="n"/>
       <c r="P78" s="6" t="n"/>
       <c r="AB78" s="6" t="n"/>
-      <c r="AC78" s="5" t="n"/>
-      <c r="AD78" s="5" t="n"/>
-      <c r="AE78" s="5" t="n"/>
+      <c r="AD78" s="6" t="n"/>
       <c r="AF78" s="5" t="n"/>
       <c r="AG78" s="6" t="n"/>
     </row>
@@ -6998,9 +7018,7 @@
       <c r="O79" s="5" t="n"/>
       <c r="P79" s="6" t="n"/>
       <c r="AB79" s="6" t="n"/>
-      <c r="AC79" s="5" t="n"/>
-      <c r="AD79" s="5" t="n"/>
-      <c r="AE79" s="5" t="n"/>
+      <c r="AD79" s="6" t="n"/>
       <c r="AF79" s="5" t="n"/>
       <c r="AG79" s="6" t="n"/>
     </row>
@@ -7009,9 +7027,7 @@
       <c r="O80" s="5" t="n"/>
       <c r="P80" s="6" t="n"/>
       <c r="AB80" s="6" t="n"/>
-      <c r="AC80" s="5" t="n"/>
-      <c r="AD80" s="5" t="n"/>
-      <c r="AE80" s="5" t="n"/>
+      <c r="AD80" s="6" t="n"/>
       <c r="AF80" s="5" t="n"/>
       <c r="AG80" s="6" t="n"/>
     </row>
@@ -7020,9 +7036,7 @@
       <c r="O81" s="5" t="n"/>
       <c r="P81" s="6" t="n"/>
       <c r="AB81" s="6" t="n"/>
-      <c r="AC81" s="5" t="n"/>
-      <c r="AD81" s="5" t="n"/>
-      <c r="AE81" s="5" t="n"/>
+      <c r="AD81" s="6" t="n"/>
       <c r="AF81" s="5" t="n"/>
       <c r="AG81" s="6" t="n"/>
     </row>
@@ -7031,9 +7045,7 @@
       <c r="O82" s="5" t="n"/>
       <c r="P82" s="6" t="n"/>
       <c r="AB82" s="6" t="n"/>
-      <c r="AC82" s="5" t="n"/>
-      <c r="AD82" s="5" t="n"/>
-      <c r="AE82" s="5" t="n"/>
+      <c r="AD82" s="6" t="n"/>
       <c r="AF82" s="5" t="n"/>
       <c r="AG82" s="6" t="n"/>
     </row>
@@ -7042,9 +7054,7 @@
       <c r="O83" s="5" t="n"/>
       <c r="P83" s="6" t="n"/>
       <c r="AB83" s="6" t="n"/>
-      <c r="AC83" s="5" t="n"/>
-      <c r="AD83" s="5" t="n"/>
-      <c r="AE83" s="5" t="n"/>
+      <c r="AD83" s="6" t="n"/>
       <c r="AF83" s="5" t="n"/>
       <c r="AG83" s="6" t="n"/>
     </row>
@@ -7053,9 +7063,7 @@
       <c r="O84" s="5" t="n"/>
       <c r="P84" s="6" t="n"/>
       <c r="AB84" s="6" t="n"/>
-      <c r="AC84" s="5" t="n"/>
-      <c r="AD84" s="5" t="n"/>
-      <c r="AE84" s="5" t="n"/>
+      <c r="AD84" s="6" t="n"/>
       <c r="AF84" s="5" t="n"/>
       <c r="AG84" s="6" t="n"/>
     </row>
@@ -7064,9 +7072,7 @@
       <c r="O85" s="5" t="n"/>
       <c r="P85" s="6" t="n"/>
       <c r="AB85" s="6" t="n"/>
-      <c r="AC85" s="5" t="n"/>
-      <c r="AD85" s="5" t="n"/>
-      <c r="AE85" s="5" t="n"/>
+      <c r="AD85" s="6" t="n"/>
       <c r="AF85" s="5" t="n"/>
       <c r="AG85" s="6" t="n"/>
     </row>
@@ -7075,9 +7081,7 @@
       <c r="O86" s="5" t="n"/>
       <c r="P86" s="6" t="n"/>
       <c r="AB86" s="6" t="n"/>
-      <c r="AC86" s="5" t="n"/>
-      <c r="AD86" s="5" t="n"/>
-      <c r="AE86" s="5" t="n"/>
+      <c r="AD86" s="6" t="n"/>
       <c r="AF86" s="5" t="n"/>
       <c r="AG86" s="6" t="n"/>
     </row>
@@ -7086,9 +7090,7 @@
       <c r="O87" s="5" t="n"/>
       <c r="P87" s="6" t="n"/>
       <c r="AB87" s="6" t="n"/>
-      <c r="AC87" s="5" t="n"/>
-      <c r="AD87" s="5" t="n"/>
-      <c r="AE87" s="5" t="n"/>
+      <c r="AD87" s="6" t="n"/>
       <c r="AF87" s="5" t="n"/>
       <c r="AG87" s="6" t="n"/>
     </row>
@@ -7097,9 +7099,7 @@
       <c r="O88" s="5" t="n"/>
       <c r="P88" s="6" t="n"/>
       <c r="AB88" s="6" t="n"/>
-      <c r="AC88" s="5" t="n"/>
-      <c r="AD88" s="5" t="n"/>
-      <c r="AE88" s="5" t="n"/>
+      <c r="AD88" s="6" t="n"/>
       <c r="AF88" s="5" t="n"/>
       <c r="AG88" s="6" t="n"/>
     </row>
@@ -7108,9 +7108,7 @@
       <c r="O89" s="5" t="n"/>
       <c r="P89" s="6" t="n"/>
       <c r="AB89" s="6" t="n"/>
-      <c r="AC89" s="5" t="n"/>
-      <c r="AD89" s="5" t="n"/>
-      <c r="AE89" s="5" t="n"/>
+      <c r="AD89" s="6" t="n"/>
       <c r="AF89" s="5" t="n"/>
       <c r="AG89" s="6" t="n"/>
     </row>
@@ -7119,9 +7117,7 @@
       <c r="O90" s="5" t="n"/>
       <c r="P90" s="6" t="n"/>
       <c r="AB90" s="6" t="n"/>
-      <c r="AC90" s="5" t="n"/>
-      <c r="AD90" s="5" t="n"/>
-      <c r="AE90" s="5" t="n"/>
+      <c r="AD90" s="6" t="n"/>
       <c r="AF90" s="5" t="n"/>
       <c r="AG90" s="6" t="n"/>
     </row>
@@ -7130,9 +7126,7 @@
       <c r="O91" s="5" t="n"/>
       <c r="P91" s="6" t="n"/>
       <c r="AB91" s="6" t="n"/>
-      <c r="AC91" s="5" t="n"/>
-      <c r="AD91" s="5" t="n"/>
-      <c r="AE91" s="5" t="n"/>
+      <c r="AD91" s="6" t="n"/>
       <c r="AF91" s="5" t="n"/>
       <c r="AG91" s="6" t="n"/>
     </row>
@@ -7141,9 +7135,7 @@
       <c r="O92" s="5" t="n"/>
       <c r="P92" s="6" t="n"/>
       <c r="AB92" s="6" t="n"/>
-      <c r="AC92" s="5" t="n"/>
-      <c r="AD92" s="5" t="n"/>
-      <c r="AE92" s="5" t="n"/>
+      <c r="AD92" s="6" t="n"/>
       <c r="AF92" s="5" t="n"/>
       <c r="AG92" s="6" t="n"/>
     </row>
@@ -7152,9 +7144,7 @@
       <c r="O93" s="5" t="n"/>
       <c r="P93" s="6" t="n"/>
       <c r="AB93" s="6" t="n"/>
-      <c r="AC93" s="5" t="n"/>
-      <c r="AD93" s="5" t="n"/>
-      <c r="AE93" s="5" t="n"/>
+      <c r="AD93" s="6" t="n"/>
       <c r="AF93" s="5" t="n"/>
       <c r="AG93" s="6" t="n"/>
     </row>
@@ -7163,9 +7153,7 @@
       <c r="O94" s="5" t="n"/>
       <c r="P94" s="6" t="n"/>
       <c r="AB94" s="6" t="n"/>
-      <c r="AC94" s="5" t="n"/>
-      <c r="AD94" s="5" t="n"/>
-      <c r="AE94" s="5" t="n"/>
+      <c r="AD94" s="6" t="n"/>
       <c r="AF94" s="5" t="n"/>
       <c r="AG94" s="6" t="n"/>
     </row>
@@ -7174,9 +7162,7 @@
       <c r="O95" s="5" t="n"/>
       <c r="P95" s="6" t="n"/>
       <c r="AB95" s="6" t="n"/>
-      <c r="AC95" s="5" t="n"/>
-      <c r="AD95" s="5" t="n"/>
-      <c r="AE95" s="5" t="n"/>
+      <c r="AD95" s="6" t="n"/>
       <c r="AF95" s="5" t="n"/>
       <c r="AG95" s="6" t="n"/>
     </row>
@@ -7185,9 +7171,7 @@
       <c r="O96" s="5" t="n"/>
       <c r="P96" s="6" t="n"/>
       <c r="AB96" s="6" t="n"/>
-      <c r="AC96" s="5" t="n"/>
-      <c r="AD96" s="5" t="n"/>
-      <c r="AE96" s="5" t="n"/>
+      <c r="AD96" s="6" t="n"/>
       <c r="AF96" s="5" t="n"/>
       <c r="AG96" s="6" t="n"/>
     </row>
@@ -7196,9 +7180,7 @@
       <c r="O97" s="5" t="n"/>
       <c r="P97" s="6" t="n"/>
       <c r="AB97" s="6" t="n"/>
-      <c r="AC97" s="5" t="n"/>
-      <c r="AD97" s="5" t="n"/>
-      <c r="AE97" s="5" t="n"/>
+      <c r="AD97" s="6" t="n"/>
       <c r="AF97" s="5" t="n"/>
       <c r="AG97" s="6" t="n"/>
     </row>
@@ -7207,9 +7189,7 @@
       <c r="O98" s="5" t="n"/>
       <c r="P98" s="6" t="n"/>
       <c r="AB98" s="6" t="n"/>
-      <c r="AC98" s="5" t="n"/>
-      <c r="AD98" s="5" t="n"/>
-      <c r="AE98" s="5" t="n"/>
+      <c r="AD98" s="6" t="n"/>
       <c r="AF98" s="5" t="n"/>
       <c r="AG98" s="6" t="n"/>
     </row>
@@ -7218,9 +7198,7 @@
       <c r="O99" s="5" t="n"/>
       <c r="P99" s="6" t="n"/>
       <c r="AB99" s="6" t="n"/>
-      <c r="AC99" s="5" t="n"/>
-      <c r="AD99" s="5" t="n"/>
-      <c r="AE99" s="5" t="n"/>
+      <c r="AD99" s="6" t="n"/>
       <c r="AF99" s="5" t="n"/>
       <c r="AG99" s="6" t="n"/>
     </row>
@@ -7229,9 +7207,7 @@
       <c r="O100" s="5" t="n"/>
       <c r="P100" s="6" t="n"/>
       <c r="AB100" s="6" t="n"/>
-      <c r="AC100" s="5" t="n"/>
-      <c r="AD100" s="5" t="n"/>
-      <c r="AE100" s="5" t="n"/>
+      <c r="AD100" s="6" t="n"/>
       <c r="AF100" s="5" t="n"/>
       <c r="AG100" s="6" t="n"/>
     </row>
@@ -7240,9 +7216,7 @@
       <c r="O101" s="5" t="n"/>
       <c r="P101" s="6" t="n"/>
       <c r="AB101" s="6" t="n"/>
-      <c r="AC101" s="5" t="n"/>
-      <c r="AD101" s="5" t="n"/>
-      <c r="AE101" s="5" t="n"/>
+      <c r="AD101" s="6" t="n"/>
       <c r="AF101" s="5" t="n"/>
       <c r="AG101" s="6" t="n"/>
     </row>
@@ -7251,9 +7225,7 @@
       <c r="O102" s="5" t="n"/>
       <c r="P102" s="6" t="n"/>
       <c r="AB102" s="6" t="n"/>
-      <c r="AC102" s="5" t="n"/>
-      <c r="AD102" s="5" t="n"/>
-      <c r="AE102" s="5" t="n"/>
+      <c r="AD102" s="6" t="n"/>
       <c r="AF102" s="5" t="n"/>
       <c r="AG102" s="6" t="n"/>
     </row>
@@ -7262,9 +7234,7 @@
       <c r="O103" s="5" t="n"/>
       <c r="P103" s="6" t="n"/>
       <c r="AB103" s="6" t="n"/>
-      <c r="AC103" s="5" t="n"/>
-      <c r="AD103" s="5" t="n"/>
-      <c r="AE103" s="5" t="n"/>
+      <c r="AD103" s="6" t="n"/>
       <c r="AF103" s="5" t="n"/>
       <c r="AG103" s="6" t="n"/>
     </row>
@@ -7273,9 +7243,7 @@
       <c r="O104" s="5" t="n"/>
       <c r="P104" s="6" t="n"/>
       <c r="AB104" s="6" t="n"/>
-      <c r="AC104" s="5" t="n"/>
-      <c r="AD104" s="5" t="n"/>
-      <c r="AE104" s="5" t="n"/>
+      <c r="AD104" s="6" t="n"/>
       <c r="AF104" s="5" t="n"/>
       <c r="AG104" s="6" t="n"/>
     </row>
@@ -7284,9 +7252,7 @@
       <c r="O105" s="5" t="n"/>
       <c r="P105" s="6" t="n"/>
       <c r="AB105" s="6" t="n"/>
-      <c r="AC105" s="5" t="n"/>
-      <c r="AD105" s="5" t="n"/>
-      <c r="AE105" s="5" t="n"/>
+      <c r="AD105" s="6" t="n"/>
       <c r="AF105" s="5" t="n"/>
       <c r="AG105" s="6" t="n"/>
     </row>
@@ -7295,9 +7261,7 @@
       <c r="O106" s="5" t="n"/>
       <c r="P106" s="6" t="n"/>
       <c r="AB106" s="6" t="n"/>
-      <c r="AC106" s="5" t="n"/>
-      <c r="AD106" s="5" t="n"/>
-      <c r="AE106" s="5" t="n"/>
+      <c r="AD106" s="6" t="n"/>
       <c r="AF106" s="5" t="n"/>
       <c r="AG106" s="6" t="n"/>
     </row>
@@ -7306,9 +7270,7 @@
       <c r="O107" s="5" t="n"/>
       <c r="P107" s="6" t="n"/>
       <c r="AB107" s="6" t="n"/>
-      <c r="AC107" s="5" t="n"/>
-      <c r="AD107" s="5" t="n"/>
-      <c r="AE107" s="5" t="n"/>
+      <c r="AD107" s="6" t="n"/>
       <c r="AF107" s="5" t="n"/>
       <c r="AG107" s="6" t="n"/>
     </row>
@@ -7317,9 +7279,7 @@
       <c r="O108" s="5" t="n"/>
       <c r="P108" s="6" t="n"/>
       <c r="AB108" s="6" t="n"/>
-      <c r="AC108" s="5" t="n"/>
-      <c r="AD108" s="5" t="n"/>
-      <c r="AE108" s="5" t="n"/>
+      <c r="AD108" s="6" t="n"/>
       <c r="AF108" s="5" t="n"/>
       <c r="AG108" s="6" t="n"/>
     </row>
@@ -7328,9 +7288,7 @@
       <c r="O109" s="5" t="n"/>
       <c r="P109" s="6" t="n"/>
       <c r="AB109" s="6" t="n"/>
-      <c r="AC109" s="5" t="n"/>
-      <c r="AD109" s="5" t="n"/>
-      <c r="AE109" s="5" t="n"/>
+      <c r="AD109" s="6" t="n"/>
       <c r="AF109" s="5" t="n"/>
       <c r="AG109" s="6" t="n"/>
     </row>
@@ -7339,9 +7297,7 @@
       <c r="O110" s="5" t="n"/>
       <c r="P110" s="6" t="n"/>
       <c r="AB110" s="6" t="n"/>
-      <c r="AC110" s="5" t="n"/>
-      <c r="AD110" s="5" t="n"/>
-      <c r="AE110" s="5" t="n"/>
+      <c r="AD110" s="6" t="n"/>
       <c r="AF110" s="5" t="n"/>
       <c r="AG110" s="6" t="n"/>
     </row>
@@ -7350,9 +7306,7 @@
       <c r="O111" s="5" t="n"/>
       <c r="P111" s="6" t="n"/>
       <c r="AB111" s="6" t="n"/>
-      <c r="AC111" s="5" t="n"/>
-      <c r="AD111" s="5" t="n"/>
-      <c r="AE111" s="5" t="n"/>
+      <c r="AD111" s="6" t="n"/>
       <c r="AF111" s="5" t="n"/>
       <c r="AG111" s="6" t="n"/>
     </row>
@@ -7361,9 +7315,7 @@
       <c r="O112" s="5" t="n"/>
       <c r="P112" s="6" t="n"/>
       <c r="AB112" s="6" t="n"/>
-      <c r="AC112" s="5" t="n"/>
-      <c r="AD112" s="5" t="n"/>
-      <c r="AE112" s="5" t="n"/>
+      <c r="AD112" s="6" t="n"/>
       <c r="AF112" s="5" t="n"/>
       <c r="AG112" s="6" t="n"/>
     </row>
@@ -7372,9 +7324,7 @@
       <c r="O113" s="5" t="n"/>
       <c r="P113" s="6" t="n"/>
       <c r="AB113" s="6" t="n"/>
-      <c r="AC113" s="5" t="n"/>
-      <c r="AD113" s="5" t="n"/>
-      <c r="AE113" s="5" t="n"/>
+      <c r="AD113" s="6" t="n"/>
       <c r="AF113" s="5" t="n"/>
       <c r="AG113" s="6" t="n"/>
     </row>
@@ -7383,9 +7333,7 @@
       <c r="O114" s="5" t="n"/>
       <c r="P114" s="6" t="n"/>
       <c r="AB114" s="6" t="n"/>
-      <c r="AC114" s="5" t="n"/>
-      <c r="AD114" s="5" t="n"/>
-      <c r="AE114" s="5" t="n"/>
+      <c r="AD114" s="6" t="n"/>
       <c r="AF114" s="5" t="n"/>
       <c r="AG114" s="6" t="n"/>
     </row>
@@ -7394,9 +7342,7 @@
       <c r="O115" s="5" t="n"/>
       <c r="P115" s="6" t="n"/>
       <c r="AB115" s="6" t="n"/>
-      <c r="AC115" s="5" t="n"/>
-      <c r="AD115" s="5" t="n"/>
-      <c r="AE115" s="5" t="n"/>
+      <c r="AD115" s="6" t="n"/>
       <c r="AF115" s="5" t="n"/>
       <c r="AG115" s="6" t="n"/>
     </row>
@@ -7405,9 +7351,7 @@
       <c r="O116" s="5" t="n"/>
       <c r="P116" s="6" t="n"/>
       <c r="AB116" s="6" t="n"/>
-      <c r="AC116" s="5" t="n"/>
-      <c r="AD116" s="5" t="n"/>
-      <c r="AE116" s="5" t="n"/>
+      <c r="AD116" s="6" t="n"/>
       <c r="AF116" s="5" t="n"/>
       <c r="AG116" s="6" t="n"/>
     </row>
@@ -7416,9 +7360,7 @@
       <c r="O117" s="5" t="n"/>
       <c r="P117" s="6" t="n"/>
       <c r="AB117" s="6" t="n"/>
-      <c r="AC117" s="5" t="n"/>
-      <c r="AD117" s="5" t="n"/>
-      <c r="AE117" s="5" t="n"/>
+      <c r="AD117" s="6" t="n"/>
       <c r="AF117" s="5" t="n"/>
       <c r="AG117" s="6" t="n"/>
     </row>
@@ -7427,9 +7369,7 @@
       <c r="O118" s="5" t="n"/>
       <c r="P118" s="6" t="n"/>
       <c r="AB118" s="6" t="n"/>
-      <c r="AC118" s="5" t="n"/>
-      <c r="AD118" s="5" t="n"/>
-      <c r="AE118" s="5" t="n"/>
+      <c r="AD118" s="6" t="n"/>
       <c r="AF118" s="5" t="n"/>
       <c r="AG118" s="6" t="n"/>
     </row>
@@ -7438,9 +7378,7 @@
       <c r="O119" s="5" t="n"/>
       <c r="P119" s="6" t="n"/>
       <c r="AB119" s="6" t="n"/>
-      <c r="AC119" s="5" t="n"/>
-      <c r="AD119" s="5" t="n"/>
-      <c r="AE119" s="5" t="n"/>
+      <c r="AD119" s="6" t="n"/>
       <c r="AF119" s="5" t="n"/>
       <c r="AG119" s="6" t="n"/>
     </row>
@@ -7449,9 +7387,7 @@
       <c r="O120" s="5" t="n"/>
       <c r="P120" s="6" t="n"/>
       <c r="AB120" s="6" t="n"/>
-      <c r="AC120" s="5" t="n"/>
-      <c r="AD120" s="5" t="n"/>
-      <c r="AE120" s="5" t="n"/>
+      <c r="AD120" s="6" t="n"/>
       <c r="AF120" s="5" t="n"/>
       <c r="AG120" s="6" t="n"/>
     </row>
@@ -7460,9 +7396,7 @@
       <c r="O121" s="5" t="n"/>
       <c r="P121" s="6" t="n"/>
       <c r="AB121" s="6" t="n"/>
-      <c r="AC121" s="5" t="n"/>
-      <c r="AD121" s="5" t="n"/>
-      <c r="AE121" s="5" t="n"/>
+      <c r="AD121" s="6" t="n"/>
       <c r="AF121" s="5" t="n"/>
       <c r="AG121" s="6" t="n"/>
     </row>
@@ -7471,9 +7405,7 @@
       <c r="O122" s="5" t="n"/>
       <c r="P122" s="6" t="n"/>
       <c r="AB122" s="6" t="n"/>
-      <c r="AC122" s="5" t="n"/>
-      <c r="AD122" s="5" t="n"/>
-      <c r="AE122" s="5" t="n"/>
+      <c r="AD122" s="6" t="n"/>
       <c r="AF122" s="5" t="n"/>
       <c r="AG122" s="6" t="n"/>
     </row>
@@ -7482,9 +7414,7 @@
       <c r="O123" s="5" t="n"/>
       <c r="P123" s="6" t="n"/>
       <c r="AB123" s="6" t="n"/>
-      <c r="AC123" s="5" t="n"/>
-      <c r="AD123" s="5" t="n"/>
-      <c r="AE123" s="5" t="n"/>
+      <c r="AD123" s="6" t="n"/>
       <c r="AF123" s="5" t="n"/>
       <c r="AG123" s="6" t="n"/>
     </row>
@@ -7493,9 +7423,7 @@
       <c r="O124" s="5" t="n"/>
       <c r="P124" s="6" t="n"/>
       <c r="AB124" s="6" t="n"/>
-      <c r="AC124" s="5" t="n"/>
-      <c r="AD124" s="5" t="n"/>
-      <c r="AE124" s="5" t="n"/>
+      <c r="AD124" s="6" t="n"/>
       <c r="AF124" s="5" t="n"/>
       <c r="AG124" s="6" t="n"/>
     </row>
@@ -7504,9 +7432,7 @@
       <c r="O125" s="5" t="n"/>
       <c r="P125" s="6" t="n"/>
       <c r="AB125" s="6" t="n"/>
-      <c r="AC125" s="5" t="n"/>
-      <c r="AD125" s="5" t="n"/>
-      <c r="AE125" s="5" t="n"/>
+      <c r="AD125" s="6" t="n"/>
       <c r="AF125" s="5" t="n"/>
       <c r="AG125" s="6" t="n"/>
     </row>
@@ -7515,9 +7441,7 @@
       <c r="O126" s="5" t="n"/>
       <c r="P126" s="6" t="n"/>
       <c r="AB126" s="6" t="n"/>
-      <c r="AC126" s="5" t="n"/>
-      <c r="AD126" s="5" t="n"/>
-      <c r="AE126" s="5" t="n"/>
+      <c r="AD126" s="6" t="n"/>
       <c r="AF126" s="5" t="n"/>
       <c r="AG126" s="6" t="n"/>
     </row>
@@ -7526,9 +7450,7 @@
       <c r="O127" s="5" t="n"/>
       <c r="P127" s="6" t="n"/>
       <c r="AB127" s="6" t="n"/>
-      <c r="AC127" s="5" t="n"/>
-      <c r="AD127" s="5" t="n"/>
-      <c r="AE127" s="5" t="n"/>
+      <c r="AD127" s="6" t="n"/>
       <c r="AF127" s="5" t="n"/>
       <c r="AG127" s="6" t="n"/>
     </row>
@@ -7537,9 +7459,7 @@
       <c r="O128" s="5" t="n"/>
       <c r="P128" s="6" t="n"/>
       <c r="AB128" s="6" t="n"/>
-      <c r="AC128" s="5" t="n"/>
-      <c r="AD128" s="5" t="n"/>
-      <c r="AE128" s="5" t="n"/>
+      <c r="AD128" s="6" t="n"/>
       <c r="AF128" s="5" t="n"/>
       <c r="AG128" s="6" t="n"/>
     </row>
@@ -7548,9 +7468,7 @@
       <c r="O129" s="5" t="n"/>
       <c r="P129" s="6" t="n"/>
       <c r="AB129" s="6" t="n"/>
-      <c r="AC129" s="5" t="n"/>
-      <c r="AD129" s="5" t="n"/>
-      <c r="AE129" s="5" t="n"/>
+      <c r="AD129" s="6" t="n"/>
       <c r="AF129" s="5" t="n"/>
       <c r="AG129" s="6" t="n"/>
     </row>
@@ -7559,9 +7477,7 @@
       <c r="O130" s="5" t="n"/>
       <c r="P130" s="6" t="n"/>
       <c r="AB130" s="6" t="n"/>
-      <c r="AC130" s="5" t="n"/>
-      <c r="AD130" s="5" t="n"/>
-      <c r="AE130" s="5" t="n"/>
+      <c r="AD130" s="6" t="n"/>
       <c r="AF130" s="5" t="n"/>
       <c r="AG130" s="6" t="n"/>
     </row>
@@ -7570,9 +7486,7 @@
       <c r="O131" s="5" t="n"/>
       <c r="P131" s="6" t="n"/>
       <c r="AB131" s="6" t="n"/>
-      <c r="AC131" s="5" t="n"/>
-      <c r="AD131" s="5" t="n"/>
-      <c r="AE131" s="5" t="n"/>
+      <c r="AD131" s="6" t="n"/>
       <c r="AF131" s="5" t="n"/>
       <c r="AG131" s="6" t="n"/>
     </row>
@@ -7581,9 +7495,7 @@
       <c r="O132" s="5" t="n"/>
       <c r="P132" s="6" t="n"/>
       <c r="AB132" s="6" t="n"/>
-      <c r="AC132" s="5" t="n"/>
-      <c r="AD132" s="5" t="n"/>
-      <c r="AE132" s="5" t="n"/>
+      <c r="AD132" s="6" t="n"/>
       <c r="AF132" s="5" t="n"/>
       <c r="AG132" s="6" t="n"/>
     </row>
@@ -7592,9 +7504,7 @@
       <c r="O133" s="5" t="n"/>
       <c r="P133" s="6" t="n"/>
       <c r="AB133" s="6" t="n"/>
-      <c r="AC133" s="5" t="n"/>
-      <c r="AD133" s="5" t="n"/>
-      <c r="AE133" s="5" t="n"/>
+      <c r="AD133" s="6" t="n"/>
       <c r="AF133" s="5" t="n"/>
       <c r="AG133" s="6" t="n"/>
     </row>
@@ -7603,9 +7513,7 @@
       <c r="O134" s="5" t="n"/>
       <c r="P134" s="6" t="n"/>
       <c r="AB134" s="6" t="n"/>
-      <c r="AC134" s="5" t="n"/>
-      <c r="AD134" s="5" t="n"/>
-      <c r="AE134" s="5" t="n"/>
+      <c r="AD134" s="6" t="n"/>
       <c r="AF134" s="5" t="n"/>
       <c r="AG134" s="6" t="n"/>
     </row>
@@ -7614,9 +7522,7 @@
       <c r="O135" s="5" t="n"/>
       <c r="P135" s="6" t="n"/>
       <c r="AB135" s="6" t="n"/>
-      <c r="AC135" s="5" t="n"/>
-      <c r="AD135" s="5" t="n"/>
-      <c r="AE135" s="5" t="n"/>
+      <c r="AD135" s="6" t="n"/>
       <c r="AF135" s="5" t="n"/>
       <c r="AG135" s="6" t="n"/>
     </row>
@@ -7625,9 +7531,7 @@
       <c r="O136" s="5" t="n"/>
       <c r="P136" s="6" t="n"/>
       <c r="AB136" s="6" t="n"/>
-      <c r="AC136" s="5" t="n"/>
-      <c r="AD136" s="5" t="n"/>
-      <c r="AE136" s="5" t="n"/>
+      <c r="AD136" s="6" t="n"/>
       <c r="AF136" s="5" t="n"/>
       <c r="AG136" s="6" t="n"/>
     </row>
@@ -7636,9 +7540,7 @@
       <c r="O137" s="5" t="n"/>
       <c r="P137" s="6" t="n"/>
       <c r="AB137" s="6" t="n"/>
-      <c r="AC137" s="5" t="n"/>
-      <c r="AD137" s="5" t="n"/>
-      <c r="AE137" s="5" t="n"/>
+      <c r="AD137" s="6" t="n"/>
       <c r="AF137" s="5" t="n"/>
       <c r="AG137" s="6" t="n"/>
     </row>
@@ -7647,9 +7549,7 @@
       <c r="O138" s="5" t="n"/>
       <c r="P138" s="6" t="n"/>
       <c r="AB138" s="6" t="n"/>
-      <c r="AC138" s="5" t="n"/>
-      <c r="AD138" s="5" t="n"/>
-      <c r="AE138" s="5" t="n"/>
+      <c r="AD138" s="6" t="n"/>
       <c r="AF138" s="5" t="n"/>
       <c r="AG138" s="6" t="n"/>
     </row>
@@ -7658,9 +7558,7 @@
       <c r="O139" s="5" t="n"/>
       <c r="P139" s="6" t="n"/>
       <c r="AB139" s="6" t="n"/>
-      <c r="AC139" s="5" t="n"/>
-      <c r="AD139" s="5" t="n"/>
-      <c r="AE139" s="5" t="n"/>
+      <c r="AD139" s="6" t="n"/>
       <c r="AF139" s="5" t="n"/>
       <c r="AG139" s="6" t="n"/>
     </row>
@@ -7669,9 +7567,7 @@
       <c r="O140" s="5" t="n"/>
       <c r="P140" s="6" t="n"/>
       <c r="AB140" s="6" t="n"/>
-      <c r="AC140" s="5" t="n"/>
-      <c r="AD140" s="5" t="n"/>
-      <c r="AE140" s="5" t="n"/>
+      <c r="AD140" s="6" t="n"/>
       <c r="AF140" s="5" t="n"/>
       <c r="AG140" s="6" t="n"/>
     </row>
@@ -7680,9 +7576,7 @@
       <c r="O141" s="5" t="n"/>
       <c r="P141" s="6" t="n"/>
       <c r="AB141" s="6" t="n"/>
-      <c r="AC141" s="5" t="n"/>
-      <c r="AD141" s="5" t="n"/>
-      <c r="AE141" s="5" t="n"/>
+      <c r="AD141" s="6" t="n"/>
       <c r="AF141" s="5" t="n"/>
       <c r="AG141" s="6" t="n"/>
     </row>
@@ -7691,9 +7585,7 @@
       <c r="O142" s="5" t="n"/>
       <c r="P142" s="6" t="n"/>
       <c r="AB142" s="6" t="n"/>
-      <c r="AC142" s="5" t="n"/>
-      <c r="AD142" s="5" t="n"/>
-      <c r="AE142" s="5" t="n"/>
+      <c r="AD142" s="6" t="n"/>
       <c r="AF142" s="5" t="n"/>
       <c r="AG142" s="6" t="n"/>
     </row>
@@ -7702,9 +7594,7 @@
       <c r="O143" s="5" t="n"/>
       <c r="P143" s="6" t="n"/>
       <c r="AB143" s="6" t="n"/>
-      <c r="AC143" s="5" t="n"/>
-      <c r="AD143" s="5" t="n"/>
-      <c r="AE143" s="5" t="n"/>
+      <c r="AD143" s="6" t="n"/>
       <c r="AF143" s="5" t="n"/>
       <c r="AG143" s="6" t="n"/>
     </row>
@@ -7713,9 +7603,7 @@
       <c r="O144" s="5" t="n"/>
       <c r="P144" s="6" t="n"/>
       <c r="AB144" s="6" t="n"/>
-      <c r="AC144" s="5" t="n"/>
-      <c r="AD144" s="5" t="n"/>
-      <c r="AE144" s="5" t="n"/>
+      <c r="AD144" s="6" t="n"/>
       <c r="AF144" s="5" t="n"/>
       <c r="AG144" s="6" t="n"/>
     </row>
@@ -7724,9 +7612,7 @@
       <c r="O145" s="5" t="n"/>
       <c r="P145" s="6" t="n"/>
       <c r="AB145" s="6" t="n"/>
-      <c r="AC145" s="5" t="n"/>
-      <c r="AD145" s="5" t="n"/>
-      <c r="AE145" s="5" t="n"/>
+      <c r="AD145" s="6" t="n"/>
       <c r="AF145" s="5" t="n"/>
       <c r="AG145" s="6" t="n"/>
     </row>
@@ -7735,9 +7621,7 @@
       <c r="O146" s="5" t="n"/>
       <c r="P146" s="6" t="n"/>
       <c r="AB146" s="6" t="n"/>
-      <c r="AC146" s="5" t="n"/>
-      <c r="AD146" s="5" t="n"/>
-      <c r="AE146" s="5" t="n"/>
+      <c r="AD146" s="6" t="n"/>
       <c r="AF146" s="5" t="n"/>
       <c r="AG146" s="6" t="n"/>
     </row>
@@ -7746,9 +7630,7 @@
       <c r="O147" s="5" t="n"/>
       <c r="P147" s="6" t="n"/>
       <c r="AB147" s="6" t="n"/>
-      <c r="AC147" s="5" t="n"/>
-      <c r="AD147" s="5" t="n"/>
-      <c r="AE147" s="5" t="n"/>
+      <c r="AD147" s="6" t="n"/>
       <c r="AF147" s="5" t="n"/>
       <c r="AG147" s="6" t="n"/>
     </row>
@@ -7757,9 +7639,7 @@
       <c r="O148" s="5" t="n"/>
       <c r="P148" s="6" t="n"/>
       <c r="AB148" s="6" t="n"/>
-      <c r="AC148" s="5" t="n"/>
-      <c r="AD148" s="5" t="n"/>
-      <c r="AE148" s="5" t="n"/>
+      <c r="AD148" s="6" t="n"/>
       <c r="AF148" s="5" t="n"/>
       <c r="AG148" s="6" t="n"/>
     </row>
@@ -7768,9 +7648,7 @@
       <c r="O149" s="5" t="n"/>
       <c r="P149" s="6" t="n"/>
       <c r="AB149" s="6" t="n"/>
-      <c r="AC149" s="5" t="n"/>
-      <c r="AD149" s="5" t="n"/>
-      <c r="AE149" s="5" t="n"/>
+      <c r="AD149" s="6" t="n"/>
       <c r="AF149" s="5" t="n"/>
       <c r="AG149" s="6" t="n"/>
     </row>
@@ -7779,9 +7657,7 @@
       <c r="O150" s="5" t="n"/>
       <c r="P150" s="6" t="n"/>
       <c r="AB150" s="6" t="n"/>
-      <c r="AC150" s="5" t="n"/>
-      <c r="AD150" s="5" t="n"/>
-      <c r="AE150" s="5" t="n"/>
+      <c r="AD150" s="6" t="n"/>
       <c r="AF150" s="5" t="n"/>
       <c r="AG150" s="6" t="n"/>
     </row>
@@ -7790,9 +7666,7 @@
       <c r="O151" s="5" t="n"/>
       <c r="P151" s="6" t="n"/>
       <c r="AB151" s="6" t="n"/>
-      <c r="AC151" s="5" t="n"/>
-      <c r="AD151" s="5" t="n"/>
-      <c r="AE151" s="5" t="n"/>
+      <c r="AD151" s="6" t="n"/>
       <c r="AF151" s="5" t="n"/>
       <c r="AG151" s="6" t="n"/>
     </row>
@@ -7801,9 +7675,7 @@
       <c r="O152" s="5" t="n"/>
       <c r="P152" s="6" t="n"/>
       <c r="AB152" s="6" t="n"/>
-      <c r="AC152" s="5" t="n"/>
-      <c r="AD152" s="5" t="n"/>
-      <c r="AE152" s="5" t="n"/>
+      <c r="AD152" s="6" t="n"/>
       <c r="AF152" s="5" t="n"/>
       <c r="AG152" s="6" t="n"/>
     </row>
@@ -7812,9 +7684,7 @@
       <c r="O153" s="5" t="n"/>
       <c r="P153" s="6" t="n"/>
       <c r="AB153" s="6" t="n"/>
-      <c r="AC153" s="5" t="n"/>
-      <c r="AD153" s="5" t="n"/>
-      <c r="AE153" s="5" t="n"/>
+      <c r="AD153" s="6" t="n"/>
       <c r="AF153" s="5" t="n"/>
       <c r="AG153" s="6" t="n"/>
     </row>
@@ -7823,9 +7693,7 @@
       <c r="O154" s="5" t="n"/>
       <c r="P154" s="6" t="n"/>
       <c r="AB154" s="6" t="n"/>
-      <c r="AC154" s="5" t="n"/>
-      <c r="AD154" s="5" t="n"/>
-      <c r="AE154" s="5" t="n"/>
+      <c r="AD154" s="6" t="n"/>
       <c r="AF154" s="5" t="n"/>
       <c r="AG154" s="6" t="n"/>
     </row>
@@ -7834,9 +7702,7 @@
       <c r="O155" s="5" t="n"/>
       <c r="P155" s="6" t="n"/>
       <c r="AB155" s="6" t="n"/>
-      <c r="AC155" s="5" t="n"/>
-      <c r="AD155" s="5" t="n"/>
-      <c r="AE155" s="5" t="n"/>
+      <c r="AD155" s="6" t="n"/>
       <c r="AF155" s="5" t="n"/>
       <c r="AG155" s="6" t="n"/>
     </row>
@@ -7845,9 +7711,7 @@
       <c r="O156" s="5" t="n"/>
       <c r="P156" s="6" t="n"/>
       <c r="AB156" s="6" t="n"/>
-      <c r="AC156" s="5" t="n"/>
-      <c r="AD156" s="5" t="n"/>
-      <c r="AE156" s="5" t="n"/>
+      <c r="AD156" s="6" t="n"/>
       <c r="AF156" s="5" t="n"/>
       <c r="AG156" s="6" t="n"/>
     </row>
@@ -7856,9 +7720,7 @@
       <c r="O157" s="5" t="n"/>
       <c r="P157" s="6" t="n"/>
       <c r="AB157" s="6" t="n"/>
-      <c r="AC157" s="5" t="n"/>
-      <c r="AD157" s="5" t="n"/>
-      <c r="AE157" s="5" t="n"/>
+      <c r="AD157" s="6" t="n"/>
       <c r="AF157" s="5" t="n"/>
       <c r="AG157" s="6" t="n"/>
     </row>
@@ -7867,9 +7729,7 @@
       <c r="O158" s="5" t="n"/>
       <c r="P158" s="6" t="n"/>
       <c r="AB158" s="6" t="n"/>
-      <c r="AC158" s="5" t="n"/>
-      <c r="AD158" s="5" t="n"/>
-      <c r="AE158" s="5" t="n"/>
+      <c r="AD158" s="6" t="n"/>
       <c r="AF158" s="5" t="n"/>
       <c r="AG158" s="6" t="n"/>
     </row>
@@ -7878,9 +7738,7 @@
       <c r="O159" s="5" t="n"/>
       <c r="P159" s="6" t="n"/>
       <c r="AB159" s="6" t="n"/>
-      <c r="AC159" s="5" t="n"/>
-      <c r="AD159" s="5" t="n"/>
-      <c r="AE159" s="5" t="n"/>
+      <c r="AD159" s="6" t="n"/>
       <c r="AF159" s="5" t="n"/>
       <c r="AG159" s="6" t="n"/>
     </row>
@@ -7889,9 +7747,7 @@
       <c r="O160" s="5" t="n"/>
       <c r="P160" s="6" t="n"/>
       <c r="AB160" s="6" t="n"/>
-      <c r="AC160" s="5" t="n"/>
-      <c r="AD160" s="5" t="n"/>
-      <c r="AE160" s="5" t="n"/>
+      <c r="AD160" s="6" t="n"/>
       <c r="AF160" s="5" t="n"/>
       <c r="AG160" s="6" t="n"/>
     </row>
@@ -7900,9 +7756,7 @@
       <c r="O161" s="5" t="n"/>
       <c r="P161" s="6" t="n"/>
       <c r="AB161" s="6" t="n"/>
-      <c r="AC161" s="5" t="n"/>
-      <c r="AD161" s="5" t="n"/>
-      <c r="AE161" s="5" t="n"/>
+      <c r="AD161" s="6" t="n"/>
       <c r="AF161" s="5" t="n"/>
       <c r="AG161" s="6" t="n"/>
     </row>
@@ -7911,9 +7765,7 @@
       <c r="O162" s="5" t="n"/>
       <c r="P162" s="6" t="n"/>
       <c r="AB162" s="6" t="n"/>
-      <c r="AC162" s="5" t="n"/>
-      <c r="AD162" s="5" t="n"/>
-      <c r="AE162" s="5" t="n"/>
+      <c r="AD162" s="6" t="n"/>
       <c r="AF162" s="5" t="n"/>
       <c r="AG162" s="6" t="n"/>
     </row>
@@ -7922,9 +7774,7 @@
       <c r="O163" s="5" t="n"/>
       <c r="P163" s="6" t="n"/>
       <c r="AB163" s="6" t="n"/>
-      <c r="AC163" s="5" t="n"/>
-      <c r="AD163" s="5" t="n"/>
-      <c r="AE163" s="5" t="n"/>
+      <c r="AD163" s="6" t="n"/>
       <c r="AF163" s="5" t="n"/>
       <c r="AG163" s="6" t="n"/>
     </row>
@@ -7933,9 +7783,7 @@
       <c r="O164" s="5" t="n"/>
       <c r="P164" s="6" t="n"/>
       <c r="AB164" s="6" t="n"/>
-      <c r="AC164" s="5" t="n"/>
-      <c r="AD164" s="5" t="n"/>
-      <c r="AE164" s="5" t="n"/>
+      <c r="AD164" s="6" t="n"/>
       <c r="AF164" s="5" t="n"/>
       <c r="AG164" s="6" t="n"/>
     </row>
@@ -7944,9 +7792,7 @@
       <c r="O165" s="5" t="n"/>
       <c r="P165" s="6" t="n"/>
       <c r="AB165" s="6" t="n"/>
-      <c r="AC165" s="5" t="n"/>
-      <c r="AD165" s="5" t="n"/>
-      <c r="AE165" s="5" t="n"/>
+      <c r="AD165" s="6" t="n"/>
       <c r="AF165" s="5" t="n"/>
       <c r="AG165" s="6" t="n"/>
     </row>
@@ -7955,9 +7801,7 @@
       <c r="O166" s="5" t="n"/>
       <c r="P166" s="6" t="n"/>
       <c r="AB166" s="6" t="n"/>
-      <c r="AC166" s="5" t="n"/>
-      <c r="AD166" s="5" t="n"/>
-      <c r="AE166" s="5" t="n"/>
+      <c r="AD166" s="6" t="n"/>
       <c r="AF166" s="5" t="n"/>
       <c r="AG166" s="6" t="n"/>
     </row>
@@ -7966,9 +7810,7 @@
       <c r="O167" s="5" t="n"/>
       <c r="P167" s="6" t="n"/>
       <c r="AB167" s="6" t="n"/>
-      <c r="AC167" s="5" t="n"/>
-      <c r="AD167" s="5" t="n"/>
-      <c r="AE167" s="5" t="n"/>
+      <c r="AD167" s="6" t="n"/>
       <c r="AF167" s="5" t="n"/>
       <c r="AG167" s="6" t="n"/>
     </row>
@@ -7977,9 +7819,7 @@
       <c r="O168" s="5" t="n"/>
       <c r="P168" s="6" t="n"/>
       <c r="AB168" s="6" t="n"/>
-      <c r="AC168" s="5" t="n"/>
-      <c r="AD168" s="5" t="n"/>
-      <c r="AE168" s="5" t="n"/>
+      <c r="AD168" s="6" t="n"/>
       <c r="AF168" s="5" t="n"/>
       <c r="AG168" s="6" t="n"/>
     </row>
@@ -7988,9 +7828,7 @@
       <c r="O169" s="5" t="n"/>
       <c r="P169" s="6" t="n"/>
       <c r="AB169" s="6" t="n"/>
-      <c r="AC169" s="5" t="n"/>
-      <c r="AD169" s="5" t="n"/>
-      <c r="AE169" s="5" t="n"/>
+      <c r="AD169" s="6" t="n"/>
       <c r="AF169" s="5" t="n"/>
       <c r="AG169" s="6" t="n"/>
     </row>
@@ -7999,9 +7837,7 @@
       <c r="O170" s="5" t="n"/>
       <c r="P170" s="6" t="n"/>
       <c r="AB170" s="6" t="n"/>
-      <c r="AC170" s="5" t="n"/>
-      <c r="AD170" s="5" t="n"/>
-      <c r="AE170" s="5" t="n"/>
+      <c r="AD170" s="6" t="n"/>
       <c r="AF170" s="5" t="n"/>
       <c r="AG170" s="6" t="n"/>
     </row>
@@ -8010,9 +7846,7 @@
       <c r="O171" s="5" t="n"/>
       <c r="P171" s="6" t="n"/>
       <c r="AB171" s="6" t="n"/>
-      <c r="AC171" s="5" t="n"/>
-      <c r="AD171" s="5" t="n"/>
-      <c r="AE171" s="5" t="n"/>
+      <c r="AD171" s="6" t="n"/>
       <c r="AF171" s="5" t="n"/>
       <c r="AG171" s="6" t="n"/>
     </row>
@@ -8021,9 +7855,7 @@
       <c r="O172" s="5" t="n"/>
       <c r="P172" s="6" t="n"/>
       <c r="AB172" s="6" t="n"/>
-      <c r="AC172" s="5" t="n"/>
-      <c r="AD172" s="5" t="n"/>
-      <c r="AE172" s="5" t="n"/>
+      <c r="AD172" s="6" t="n"/>
       <c r="AF172" s="5" t="n"/>
       <c r="AG172" s="6" t="n"/>
     </row>
@@ -8032,9 +7864,7 @@
       <c r="O173" s="5" t="n"/>
       <c r="P173" s="6" t="n"/>
       <c r="AB173" s="6" t="n"/>
-      <c r="AC173" s="5" t="n"/>
-      <c r="AD173" s="5" t="n"/>
-      <c r="AE173" s="5" t="n"/>
+      <c r="AD173" s="6" t="n"/>
       <c r="AF173" s="5" t="n"/>
       <c r="AG173" s="6" t="n"/>
     </row>
@@ -8043,9 +7873,7 @@
       <c r="O174" s="5" t="n"/>
       <c r="P174" s="6" t="n"/>
       <c r="AB174" s="6" t="n"/>
-      <c r="AC174" s="5" t="n"/>
-      <c r="AD174" s="5" t="n"/>
-      <c r="AE174" s="5" t="n"/>
+      <c r="AD174" s="6" t="n"/>
       <c r="AF174" s="5" t="n"/>
       <c r="AG174" s="6" t="n"/>
     </row>
@@ -8054,9 +7882,7 @@
       <c r="O175" s="5" t="n"/>
       <c r="P175" s="6" t="n"/>
       <c r="AB175" s="6" t="n"/>
-      <c r="AC175" s="5" t="n"/>
-      <c r="AD175" s="5" t="n"/>
-      <c r="AE175" s="5" t="n"/>
+      <c r="AD175" s="6" t="n"/>
       <c r="AF175" s="5" t="n"/>
       <c r="AG175" s="6" t="n"/>
     </row>
@@ -8065,9 +7891,7 @@
       <c r="O176" s="5" t="n"/>
       <c r="P176" s="6" t="n"/>
       <c r="AB176" s="6" t="n"/>
-      <c r="AC176" s="5" t="n"/>
-      <c r="AD176" s="5" t="n"/>
-      <c r="AE176" s="5" t="n"/>
+      <c r="AD176" s="6" t="n"/>
       <c r="AF176" s="5" t="n"/>
       <c r="AG176" s="6" t="n"/>
     </row>
@@ -8076,9 +7900,7 @@
       <c r="O177" s="5" t="n"/>
       <c r="P177" s="6" t="n"/>
       <c r="AB177" s="6" t="n"/>
-      <c r="AC177" s="5" t="n"/>
-      <c r="AD177" s="5" t="n"/>
-      <c r="AE177" s="5" t="n"/>
+      <c r="AD177" s="6" t="n"/>
       <c r="AF177" s="5" t="n"/>
       <c r="AG177" s="6" t="n"/>
     </row>
@@ -8087,9 +7909,7 @@
       <c r="O178" s="5" t="n"/>
       <c r="P178" s="6" t="n"/>
       <c r="AB178" s="6" t="n"/>
-      <c r="AC178" s="5" t="n"/>
-      <c r="AD178" s="5" t="n"/>
-      <c r="AE178" s="5" t="n"/>
+      <c r="AD178" s="6" t="n"/>
       <c r="AF178" s="5" t="n"/>
       <c r="AG178" s="6" t="n"/>
     </row>
@@ -8098,9 +7918,7 @@
       <c r="O179" s="5" t="n"/>
       <c r="P179" s="6" t="n"/>
       <c r="AB179" s="6" t="n"/>
-      <c r="AC179" s="5" t="n"/>
-      <c r="AD179" s="5" t="n"/>
-      <c r="AE179" s="5" t="n"/>
+      <c r="AD179" s="6" t="n"/>
       <c r="AF179" s="5" t="n"/>
       <c r="AG179" s="6" t="n"/>
     </row>
@@ -8109,9 +7927,7 @@
       <c r="O180" s="5" t="n"/>
       <c r="P180" s="6" t="n"/>
       <c r="AB180" s="6" t="n"/>
-      <c r="AC180" s="5" t="n"/>
-      <c r="AD180" s="5" t="n"/>
-      <c r="AE180" s="5" t="n"/>
+      <c r="AD180" s="6" t="n"/>
       <c r="AF180" s="5" t="n"/>
       <c r="AG180" s="6" t="n"/>
     </row>
@@ -8120,9 +7936,7 @@
       <c r="O181" s="5" t="n"/>
       <c r="P181" s="6" t="n"/>
       <c r="AB181" s="6" t="n"/>
-      <c r="AC181" s="5" t="n"/>
-      <c r="AD181" s="5" t="n"/>
-      <c r="AE181" s="5" t="n"/>
+      <c r="AD181" s="6" t="n"/>
       <c r="AF181" s="5" t="n"/>
       <c r="AG181" s="6" t="n"/>
     </row>
@@ -8131,9 +7945,7 @@
       <c r="O182" s="5" t="n"/>
       <c r="P182" s="6" t="n"/>
       <c r="AB182" s="6" t="n"/>
-      <c r="AC182" s="5" t="n"/>
-      <c r="AD182" s="5" t="n"/>
-      <c r="AE182" s="5" t="n"/>
+      <c r="AD182" s="6" t="n"/>
       <c r="AF182" s="5" t="n"/>
       <c r="AG182" s="6" t="n"/>
     </row>
@@ -8142,9 +7954,7 @@
       <c r="O183" s="5" t="n"/>
       <c r="P183" s="6" t="n"/>
       <c r="AB183" s="6" t="n"/>
-      <c r="AC183" s="5" t="n"/>
-      <c r="AD183" s="5" t="n"/>
-      <c r="AE183" s="5" t="n"/>
+      <c r="AD183" s="6" t="n"/>
       <c r="AF183" s="5" t="n"/>
       <c r="AG183" s="6" t="n"/>
     </row>
@@ -8153,9 +7963,7 @@
       <c r="O184" s="5" t="n"/>
       <c r="P184" s="6" t="n"/>
       <c r="AB184" s="6" t="n"/>
-      <c r="AC184" s="5" t="n"/>
-      <c r="AD184" s="5" t="n"/>
-      <c r="AE184" s="5" t="n"/>
+      <c r="AD184" s="6" t="n"/>
       <c r="AF184" s="5" t="n"/>
       <c r="AG184" s="6" t="n"/>
     </row>
@@ -8164,9 +7972,7 @@
       <c r="O185" s="5" t="n"/>
       <c r="P185" s="6" t="n"/>
       <c r="AB185" s="6" t="n"/>
-      <c r="AC185" s="5" t="n"/>
-      <c r="AD185" s="5" t="n"/>
-      <c r="AE185" s="5" t="n"/>
+      <c r="AD185" s="6" t="n"/>
       <c r="AF185" s="5" t="n"/>
       <c r="AG185" s="6" t="n"/>
     </row>
@@ -8175,9 +7981,7 @@
       <c r="O186" s="5" t="n"/>
       <c r="P186" s="6" t="n"/>
       <c r="AB186" s="6" t="n"/>
-      <c r="AC186" s="5" t="n"/>
-      <c r="AD186" s="5" t="n"/>
-      <c r="AE186" s="5" t="n"/>
+      <c r="AD186" s="6" t="n"/>
       <c r="AF186" s="5" t="n"/>
       <c r="AG186" s="6" t="n"/>
     </row>
@@ -8186,9 +7990,7 @@
       <c r="O187" s="5" t="n"/>
       <c r="P187" s="6" t="n"/>
       <c r="AB187" s="6" t="n"/>
-      <c r="AC187" s="5" t="n"/>
-      <c r="AD187" s="5" t="n"/>
-      <c r="AE187" s="5" t="n"/>
+      <c r="AD187" s="6" t="n"/>
       <c r="AF187" s="5" t="n"/>
       <c r="AG187" s="6" t="n"/>
     </row>
@@ -8197,9 +7999,7 @@
       <c r="O188" s="5" t="n"/>
       <c r="P188" s="6" t="n"/>
       <c r="AB188" s="6" t="n"/>
-      <c r="AC188" s="5" t="n"/>
-      <c r="AD188" s="5" t="n"/>
-      <c r="AE188" s="5" t="n"/>
+      <c r="AD188" s="6" t="n"/>
       <c r="AF188" s="5" t="n"/>
       <c r="AG188" s="6" t="n"/>
     </row>
@@ -8208,9 +8008,7 @@
       <c r="O189" s="5" t="n"/>
       <c r="P189" s="6" t="n"/>
       <c r="AB189" s="6" t="n"/>
-      <c r="AC189" s="5" t="n"/>
-      <c r="AD189" s="5" t="n"/>
-      <c r="AE189" s="5" t="n"/>
+      <c r="AD189" s="6" t="n"/>
       <c r="AF189" s="5" t="n"/>
       <c r="AG189" s="6" t="n"/>
     </row>
@@ -8219,9 +8017,7 @@
       <c r="O190" s="5" t="n"/>
       <c r="P190" s="6" t="n"/>
       <c r="AB190" s="6" t="n"/>
-      <c r="AC190" s="5" t="n"/>
-      <c r="AD190" s="5" t="n"/>
-      <c r="AE190" s="5" t="n"/>
+      <c r="AD190" s="6" t="n"/>
       <c r="AF190" s="5" t="n"/>
       <c r="AG190" s="6" t="n"/>
     </row>
@@ -8230,9 +8026,7 @@
       <c r="O191" s="5" t="n"/>
       <c r="P191" s="6" t="n"/>
       <c r="AB191" s="6" t="n"/>
-      <c r="AC191" s="5" t="n"/>
-      <c r="AD191" s="5" t="n"/>
-      <c r="AE191" s="5" t="n"/>
+      <c r="AD191" s="6" t="n"/>
       <c r="AF191" s="5" t="n"/>
       <c r="AG191" s="6" t="n"/>
     </row>
@@ -8241,9 +8035,7 @@
       <c r="O192" s="5" t="n"/>
       <c r="P192" s="6" t="n"/>
       <c r="AB192" s="6" t="n"/>
-      <c r="AC192" s="5" t="n"/>
-      <c r="AD192" s="5" t="n"/>
-      <c r="AE192" s="5" t="n"/>
+      <c r="AD192" s="6" t="n"/>
       <c r="AF192" s="5" t="n"/>
       <c r="AG192" s="6" t="n"/>
     </row>
@@ -8252,9 +8044,7 @@
       <c r="O193" s="5" t="n"/>
       <c r="P193" s="6" t="n"/>
       <c r="AB193" s="6" t="n"/>
-      <c r="AC193" s="5" t="n"/>
-      <c r="AD193" s="5" t="n"/>
-      <c r="AE193" s="5" t="n"/>
+      <c r="AD193" s="6" t="n"/>
       <c r="AF193" s="5" t="n"/>
       <c r="AG193" s="6" t="n"/>
     </row>
@@ -8263,9 +8053,7 @@
       <c r="O194" s="5" t="n"/>
       <c r="P194" s="6" t="n"/>
       <c r="AB194" s="6" t="n"/>
-      <c r="AC194" s="5" t="n"/>
-      <c r="AD194" s="5" t="n"/>
-      <c r="AE194" s="5" t="n"/>
+      <c r="AD194" s="6" t="n"/>
       <c r="AF194" s="5" t="n"/>
       <c r="AG194" s="6" t="n"/>
     </row>
@@ -8274,9 +8062,7 @@
       <c r="O195" s="5" t="n"/>
       <c r="P195" s="6" t="n"/>
       <c r="AB195" s="6" t="n"/>
-      <c r="AC195" s="5" t="n"/>
-      <c r="AD195" s="5" t="n"/>
-      <c r="AE195" s="5" t="n"/>
+      <c r="AD195" s="6" t="n"/>
       <c r="AF195" s="5" t="n"/>
       <c r="AG195" s="6" t="n"/>
     </row>
@@ -8285,9 +8071,7 @@
       <c r="O196" s="5" t="n"/>
       <c r="P196" s="6" t="n"/>
       <c r="AB196" s="6" t="n"/>
-      <c r="AC196" s="5" t="n"/>
-      <c r="AD196" s="5" t="n"/>
-      <c r="AE196" s="5" t="n"/>
+      <c r="AD196" s="6" t="n"/>
       <c r="AF196" s="5" t="n"/>
       <c r="AG196" s="6" t="n"/>
     </row>
@@ -8296,9 +8080,7 @@
       <c r="O197" s="5" t="n"/>
       <c r="P197" s="6" t="n"/>
       <c r="AB197" s="6" t="n"/>
-      <c r="AC197" s="5" t="n"/>
-      <c r="AD197" s="5" t="n"/>
-      <c r="AE197" s="5" t="n"/>
+      <c r="AD197" s="6" t="n"/>
       <c r="AF197" s="5" t="n"/>
       <c r="AG197" s="6" t="n"/>
     </row>
@@ -8307,9 +8089,7 @@
       <c r="O198" s="5" t="n"/>
       <c r="P198" s="6" t="n"/>
       <c r="AB198" s="6" t="n"/>
-      <c r="AC198" s="5" t="n"/>
-      <c r="AD198" s="5" t="n"/>
-      <c r="AE198" s="5" t="n"/>
+      <c r="AD198" s="6" t="n"/>
       <c r="AF198" s="5" t="n"/>
       <c r="AG198" s="6" t="n"/>
     </row>
@@ -8318,9 +8098,7 @@
       <c r="O199" s="5" t="n"/>
       <c r="P199" s="6" t="n"/>
       <c r="AB199" s="6" t="n"/>
-      <c r="AC199" s="5" t="n"/>
-      <c r="AD199" s="5" t="n"/>
-      <c r="AE199" s="5" t="n"/>
+      <c r="AD199" s="6" t="n"/>
       <c r="AF199" s="5" t="n"/>
       <c r="AG199" s="6" t="n"/>
     </row>
@@ -8329,9 +8107,7 @@
       <c r="O200" s="5" t="n"/>
       <c r="P200" s="6" t="n"/>
       <c r="AB200" s="6" t="n"/>
-      <c r="AC200" s="5" t="n"/>
-      <c r="AD200" s="5" t="n"/>
-      <c r="AE200" s="5" t="n"/>
+      <c r="AD200" s="6" t="n"/>
       <c r="AF200" s="5" t="n"/>
       <c r="AG200" s="6" t="n"/>
     </row>
@@ -8340,9 +8116,7 @@
       <c r="O201" s="5" t="n"/>
       <c r="P201" s="6" t="n"/>
       <c r="AB201" s="6" t="n"/>
-      <c r="AC201" s="5" t="n"/>
-      <c r="AD201" s="5" t="n"/>
-      <c r="AE201" s="5" t="n"/>
+      <c r="AD201" s="6" t="n"/>
       <c r="AF201" s="5" t="n"/>
       <c r="AG201" s="6" t="n"/>
     </row>
@@ -8351,9 +8125,7 @@
       <c r="O202" s="5" t="n"/>
       <c r="P202" s="6" t="n"/>
       <c r="AB202" s="6" t="n"/>
-      <c r="AC202" s="5" t="n"/>
-      <c r="AD202" s="5" t="n"/>
-      <c r="AE202" s="5" t="n"/>
+      <c r="AD202" s="6" t="n"/>
       <c r="AF202" s="5" t="n"/>
       <c r="AG202" s="6" t="n"/>
     </row>
@@ -8362,9 +8134,7 @@
       <c r="O203" s="5" t="n"/>
       <c r="P203" s="6" t="n"/>
       <c r="AB203" s="6" t="n"/>
-      <c r="AC203" s="5" t="n"/>
-      <c r="AD203" s="5" t="n"/>
-      <c r="AE203" s="5" t="n"/>
+      <c r="AD203" s="6" t="n"/>
       <c r="AF203" s="5" t="n"/>
       <c r="AG203" s="6" t="n"/>
     </row>
@@ -8852,11 +8622,7 @@
           <t>Familia</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
+      <c r="B35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -8871,11 +8637,7 @@
           <t>ID familia ampliada</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
+      <c r="B37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8883,11 +8645,7 @@
           <t>Familia Ampliada</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -11165,7 +10923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11203,16 +10961,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nombre de la residencia/hogar</t>
+          <t>Fecha de inicio MPE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mpe_nombre_de_la_residencia_existe_en_archivo</t>
+          <t>mpe_fecha_de_inicio_mpe_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -11223,16 +10981,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Familia Ampliada</t>
+          <t>Días de permanencia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mpe_familia_ampliada_comparar_valor</t>
+          <t>rango_dias_de_permanencia</t>
         </is>
       </c>
     </row>
@@ -11287,12 +11045,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Familia</t>
+          <t>Días de permanencia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>mpe_familia_comparar_valor</t>
+          <t>rango_dias_de_permanencia</t>
         </is>
       </c>
     </row>
@@ -11303,16 +11061,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fecha de inicio MPE</t>
+          <t>Fecha del relevamiento</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mpe_fecha_de_inicio_mpe_comparar_valor</t>
+          <t>mpe_fecha_del_relevamiento_comparar_valor</t>
         </is>
       </c>
     </row>
@@ -11327,12 +11085,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>¿Posee CUD?</t>
+          <t>Días de permanencia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mpe_posee_cud_obligatorio_si</t>
+          <t>rango_dias_de_permanencia</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11101,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -11363,16 +11121,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Edad</t>
+          <t>Días de permanencia</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>mpe_edad_rango</t>
+          <t>rango_dias_de_permanencia</t>
         </is>
       </c>
     </row>
@@ -11383,94 +11141,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ID familia ampliada</t>
+          <t>Fecha del relevamiento</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>mpe_id_familia_ampliada_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>27</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ID familia ampliada</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>mpe_id_familia_ampliada_comparar_valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>27</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Días de permanencia</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>rango_dias_de_permanencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>30</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Días de permanencia</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>rango_dias_de_permanencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MPE</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>33</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Fecha del relevamiento</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>mpe_fecha_del_relevamiento_comparar_valor</t>
         </is>
